--- a/data/raw/SOX.xlsx
+++ b/data/raw/SOX.xlsx
@@ -468,19 +468,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45834</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>5541.4599609375</v>
+        <v>5541.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>5553.2900390625</v>
+        <v>5613.919921875</v>
       </c>
       <c r="D2" t="n">
-        <v>5495.22021484375</v>
+        <v>5519.47998046875</v>
       </c>
       <c r="E2" t="n">
-        <v>5530.4599609375</v>
+        <v>5596.47021484375</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -488,19 +488,19 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45835</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>5544.990234375</v>
+        <v>5641.22021484375</v>
       </c>
       <c r="C3" t="n">
-        <v>5588.52001953125</v>
+        <v>5676.68017578125</v>
       </c>
       <c r="D3" t="n">
-        <v>5488.68017578125</v>
+        <v>5572.8798828125</v>
       </c>
       <c r="E3" t="n">
-        <v>5549.4599609375</v>
+        <v>5591.43994140625</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -508,19 +508,19 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45838</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>5546.5400390625</v>
+        <v>5665.990234375</v>
       </c>
       <c r="C4" t="n">
-        <v>5571.39013671875</v>
+        <v>5722.3798828125</v>
       </c>
       <c r="D4" t="n">
-        <v>5520.27978515625</v>
+        <v>5618.97021484375</v>
       </c>
       <c r="E4" t="n">
-        <v>5564.169921875</v>
+        <v>5665.8701171875</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -528,19 +528,19 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45839</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>5507.5</v>
+        <v>5708.27978515625</v>
       </c>
       <c r="C5" t="n">
-        <v>5543.93017578125</v>
+        <v>5724.0498046875</v>
       </c>
       <c r="D5" t="n">
-        <v>5429.16015625</v>
+        <v>5657.89013671875</v>
       </c>
       <c r="E5" t="n">
-        <v>5512.10986328125</v>
+        <v>5712.2998046875</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -548,19 +548,19 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45840</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>5611.0498046875</v>
+        <v>5696.2900390625</v>
       </c>
       <c r="C6" t="n">
-        <v>5627.64013671875</v>
+        <v>5718.75</v>
       </c>
       <c r="D6" t="n">
-        <v>5490.56005859375</v>
+        <v>5659.08984375</v>
       </c>
       <c r="E6" t="n">
-        <v>5503.259765625</v>
+        <v>5677.919921875</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -568,19 +568,19 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45841</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>5647.1201171875</v>
+        <v>5646.72021484375</v>
       </c>
       <c r="C7" t="n">
-        <v>5668.14013671875</v>
+        <v>5671.2001953125</v>
       </c>
       <c r="D7" t="n">
-        <v>5630.240234375</v>
+        <v>5568.490234375</v>
       </c>
       <c r="E7" t="n">
-        <v>5633.08984375</v>
+        <v>5651.77978515625</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -588,19 +588,19 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45845</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>5541.2001953125</v>
+        <v>5718.60986328125</v>
       </c>
       <c r="C8" t="n">
-        <v>5613.919921875</v>
+        <v>5791.81005859375</v>
       </c>
       <c r="D8" t="n">
-        <v>5519.47998046875</v>
+        <v>5714.35009765625</v>
       </c>
       <c r="E8" t="n">
-        <v>5596.47021484375</v>
+        <v>5778.02978515625</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -608,19 +608,19 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45846</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>5641.22021484375</v>
+        <v>5696.2099609375</v>
       </c>
       <c r="C9" t="n">
-        <v>5676.68017578125</v>
+        <v>5698.14013671875</v>
       </c>
       <c r="D9" t="n">
-        <v>5572.8798828125</v>
+        <v>5560.06982421875</v>
       </c>
       <c r="E9" t="n">
-        <v>5591.43994140625</v>
+        <v>5659.2998046875</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -628,19 +628,19 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45847</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>5665.990234375</v>
+        <v>5737.64013671875</v>
       </c>
       <c r="C10" t="n">
-        <v>5722.3798828125</v>
+        <v>5755.080078125</v>
       </c>
       <c r="D10" t="n">
-        <v>5618.97021484375</v>
+        <v>5670.14990234375</v>
       </c>
       <c r="E10" t="n">
-        <v>5665.8701171875</v>
+        <v>5696.7900390625</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -648,19 +648,19 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45848</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>5708.27978515625</v>
+        <v>5732.6201171875</v>
       </c>
       <c r="C11" t="n">
-        <v>5724.0498046875</v>
+        <v>5776.31005859375</v>
       </c>
       <c r="D11" t="n">
-        <v>5657.89013671875</v>
+        <v>5695.0498046875</v>
       </c>
       <c r="E11" t="n">
-        <v>5712.2998046875</v>
+        <v>5754.89013671875</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -668,19 +668,19 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45849</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>5696.2900390625</v>
+        <v>5739.419921875</v>
       </c>
       <c r="C12" t="n">
-        <v>5718.75</v>
+        <v>5808.60009765625</v>
       </c>
       <c r="D12" t="n">
-        <v>5659.08984375</v>
+        <v>5737.81982421875</v>
       </c>
       <c r="E12" t="n">
-        <v>5677.919921875</v>
+        <v>5754.740234375</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -688,19 +688,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45852</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>5646.72021484375</v>
+        <v>5638.7099609375</v>
       </c>
       <c r="C13" t="n">
-        <v>5671.2001953125</v>
+        <v>5721.02001953125</v>
       </c>
       <c r="D13" t="n">
-        <v>5568.490234375</v>
+        <v>5580.2998046875</v>
       </c>
       <c r="E13" t="n">
-        <v>5651.77978515625</v>
+        <v>5717.72021484375</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -708,19 +708,19 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45853</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>5718.60986328125</v>
+        <v>5637.7900390625</v>
       </c>
       <c r="C14" t="n">
-        <v>5791.81005859375</v>
+        <v>5642.14990234375</v>
       </c>
       <c r="D14" t="n">
-        <v>5714.35009765625</v>
+        <v>5564.60986328125</v>
       </c>
       <c r="E14" t="n">
-        <v>5778.02978515625</v>
+        <v>5613.68994140625</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -728,19 +728,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45854</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>5696.2099609375</v>
+        <v>5644.3701171875</v>
       </c>
       <c r="C15" t="n">
-        <v>5698.14013671875</v>
+        <v>5657.580078125</v>
       </c>
       <c r="D15" t="n">
-        <v>5560.06982421875</v>
+        <v>5595.240234375</v>
       </c>
       <c r="E15" t="n">
-        <v>5659.2998046875</v>
+        <v>5645.33984375</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -748,19 +748,19 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45855</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>5737.64013671875</v>
+        <v>5645.85986328125</v>
       </c>
       <c r="C16" t="n">
-        <v>5755.080078125</v>
+        <v>5650.16015625</v>
       </c>
       <c r="D16" t="n">
-        <v>5670.14990234375</v>
+        <v>5589.97998046875</v>
       </c>
       <c r="E16" t="n">
-        <v>5696.7900390625</v>
+        <v>5601.52001953125</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -768,19 +768,19 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45856</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>5732.6201171875</v>
+        <v>5737.10009765625</v>
       </c>
       <c r="C17" t="n">
-        <v>5776.31005859375</v>
+        <v>5738.919921875</v>
       </c>
       <c r="D17" t="n">
-        <v>5695.0498046875</v>
+        <v>5695.93017578125</v>
       </c>
       <c r="E17" t="n">
-        <v>5754.89013671875</v>
+        <v>5704.89013671875</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -788,19 +788,19 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>5739.419921875</v>
+        <v>5739.7900390625</v>
       </c>
       <c r="C18" t="n">
-        <v>5808.60009765625</v>
+        <v>5819.8701171875</v>
       </c>
       <c r="D18" t="n">
-        <v>5737.81982421875</v>
+        <v>5706.02978515625</v>
       </c>
       <c r="E18" t="n">
-        <v>5754.740234375</v>
+        <v>5784.02978515625</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -808,19 +808,19 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45860</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>5638.7099609375</v>
+        <v>5787.31982421875</v>
       </c>
       <c r="C19" t="n">
-        <v>5721.02001953125</v>
+        <v>5820.5400390625</v>
       </c>
       <c r="D19" t="n">
-        <v>5580.2998046875</v>
+        <v>5738.64990234375</v>
       </c>
       <c r="E19" t="n">
-        <v>5717.72021484375</v>
+        <v>5788.83984375</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -828,19 +828,19 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45861</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>5637.7900390625</v>
+        <v>5607.919921875</v>
       </c>
       <c r="C20" t="n">
-        <v>5642.14990234375</v>
+        <v>5730.419921875</v>
       </c>
       <c r="D20" t="n">
-        <v>5564.60986328125</v>
+        <v>5558.10986328125</v>
       </c>
       <c r="E20" t="n">
-        <v>5613.68994140625</v>
+        <v>5721.580078125</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -848,19 +848,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45862</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>5644.3701171875</v>
+        <v>5527.60986328125</v>
       </c>
       <c r="C21" t="n">
-        <v>5657.580078125</v>
+        <v>5583.43017578125</v>
       </c>
       <c r="D21" t="n">
-        <v>5595.240234375</v>
+        <v>5418.31982421875</v>
       </c>
       <c r="E21" t="n">
-        <v>5645.33984375</v>
+        <v>5501.91015625</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -868,19 +868,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45863</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>5645.85986328125</v>
+        <v>5624.41015625</v>
       </c>
       <c r="C22" t="n">
-        <v>5650.16015625</v>
+        <v>5624.85986328125</v>
       </c>
       <c r="D22" t="n">
-        <v>5589.97998046875</v>
+        <v>5550.1201171875</v>
       </c>
       <c r="E22" t="n">
-        <v>5601.52001953125</v>
+        <v>5575.830078125</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -888,19 +888,19 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45866</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>5737.10009765625</v>
+        <v>5561.68994140625</v>
       </c>
       <c r="C23" t="n">
-        <v>5738.919921875</v>
+        <v>5651</v>
       </c>
       <c r="D23" t="n">
-        <v>5695.93017578125</v>
+        <v>5501.43017578125</v>
       </c>
       <c r="E23" t="n">
-        <v>5704.89013671875</v>
+        <v>5633.06005859375</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -908,19 +908,19 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45867</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>5739.7900390625</v>
+        <v>5550.2998046875</v>
       </c>
       <c r="C24" t="n">
-        <v>5819.8701171875</v>
+        <v>5561.43994140625</v>
       </c>
       <c r="D24" t="n">
-        <v>5706.02978515625</v>
+        <v>5474.509765625</v>
       </c>
       <c r="E24" t="n">
-        <v>5784.02978515625</v>
+        <v>5525.58984375</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -928,19 +928,19 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45868</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>5787.31982421875</v>
+        <v>5633.7001953125</v>
       </c>
       <c r="C25" t="n">
-        <v>5820.5400390625</v>
+        <v>5701.509765625</v>
       </c>
       <c r="D25" t="n">
-        <v>5738.64990234375</v>
+        <v>5588.3701171875</v>
       </c>
       <c r="E25" t="n">
-        <v>5788.83984375</v>
+        <v>5675.1201171875</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -948,19 +948,19 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45869</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>5607.919921875</v>
+        <v>5678.02001953125</v>
       </c>
       <c r="C26" t="n">
-        <v>5730.419921875</v>
+        <v>5682.10009765625</v>
       </c>
       <c r="D26" t="n">
-        <v>5558.10986328125</v>
+        <v>5616.990234375</v>
       </c>
       <c r="E26" t="n">
-        <v>5721.580078125</v>
+        <v>5629.47021484375</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -968,19 +968,19 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45870</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>5527.60986328125</v>
+        <v>5670.3701171875</v>
       </c>
       <c r="C27" t="n">
-        <v>5583.43017578125</v>
+        <v>5763.31982421875</v>
       </c>
       <c r="D27" t="n">
-        <v>5418.31982421875</v>
+        <v>5660.22998046875</v>
       </c>
       <c r="E27" t="n">
-        <v>5501.91015625</v>
+        <v>5722.080078125</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -988,19 +988,19 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45873</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>5624.41015625</v>
+        <v>5840.08984375</v>
       </c>
       <c r="C28" t="n">
-        <v>5624.85986328125</v>
+        <v>5842.52001953125</v>
       </c>
       <c r="D28" t="n">
-        <v>5550.1201171875</v>
+        <v>5682.5400390625</v>
       </c>
       <c r="E28" t="n">
-        <v>5575.830078125</v>
+        <v>5710.10986328125</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1008,19 +1008,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45874</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>5561.68994140625</v>
+        <v>5892.60986328125</v>
       </c>
       <c r="C29" t="n">
-        <v>5651</v>
+        <v>5907.9599609375</v>
       </c>
       <c r="D29" t="n">
-        <v>5501.43017578125</v>
+        <v>5835.60986328125</v>
       </c>
       <c r="E29" t="n">
-        <v>5633.06005859375</v>
+        <v>5875.4501953125</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1028,19 +1028,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45875</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>5550.2998046875</v>
+        <v>5885.490234375</v>
       </c>
       <c r="C30" t="n">
-        <v>5561.43994140625</v>
+        <v>5904.60009765625</v>
       </c>
       <c r="D30" t="n">
-        <v>5474.509765625</v>
+        <v>5787.2099609375</v>
       </c>
       <c r="E30" t="n">
-        <v>5525.58984375</v>
+        <v>5828.06982421875</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1048,19 +1048,19 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45876</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>5633.7001953125</v>
+        <v>5752.740234375</v>
       </c>
       <c r="C31" t="n">
-        <v>5701.509765625</v>
+        <v>5832.6298828125</v>
       </c>
       <c r="D31" t="n">
-        <v>5588.3701171875</v>
+        <v>5737.02978515625</v>
       </c>
       <c r="E31" t="n">
-        <v>5675.1201171875</v>
+        <v>5830.18017578125</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1068,19 +1068,19 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>5678.02001953125</v>
+        <v>5776.31005859375</v>
       </c>
       <c r="C32" t="n">
-        <v>5682.10009765625</v>
+        <v>5781</v>
       </c>
       <c r="D32" t="n">
-        <v>5616.990234375</v>
+        <v>5738.5498046875</v>
       </c>
       <c r="E32" t="n">
-        <v>5629.47021484375</v>
+        <v>5742.490234375</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1088,19 +1088,19 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45880</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>5670.3701171875</v>
+        <v>5671.509765625</v>
       </c>
       <c r="C33" t="n">
-        <v>5763.31982421875</v>
+        <v>5797.9599609375</v>
       </c>
       <c r="D33" t="n">
-        <v>5660.22998046875</v>
+        <v>5664.93017578125</v>
       </c>
       <c r="E33" t="n">
-        <v>5722.080078125</v>
+        <v>5777.66015625</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1108,19 +1108,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45881</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>5840.08984375</v>
+        <v>5630.81982421875</v>
       </c>
       <c r="C34" t="n">
-        <v>5842.52001953125</v>
+        <v>5644.31005859375</v>
       </c>
       <c r="D34" t="n">
-        <v>5682.5400390625</v>
+        <v>5480.0498046875</v>
       </c>
       <c r="E34" t="n">
-        <v>5710.10986328125</v>
+        <v>5642.89990234375</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1128,19 +1128,19 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45882</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>5892.60986328125</v>
+        <v>5603.259765625</v>
       </c>
       <c r="C35" t="n">
-        <v>5907.9599609375</v>
+        <v>5643.4501953125</v>
       </c>
       <c r="D35" t="n">
-        <v>5835.60986328125</v>
+        <v>5574.259765625</v>
       </c>
       <c r="E35" t="n">
-        <v>5875.4501953125</v>
+        <v>5607.6201171875</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1148,19 +1148,19 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45883</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>5885.490234375</v>
+        <v>5754.4599609375</v>
       </c>
       <c r="C36" t="n">
-        <v>5904.60009765625</v>
+        <v>5818.22998046875</v>
       </c>
       <c r="D36" t="n">
-        <v>5787.2099609375</v>
+        <v>5598.8798828125</v>
       </c>
       <c r="E36" t="n">
-        <v>5828.06982421875</v>
+        <v>5612.31982421875</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -1168,19 +1168,19 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45884</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>5752.740234375</v>
+        <v>5756.2998046875</v>
       </c>
       <c r="C37" t="n">
-        <v>5832.6298828125</v>
+        <v>5784.60009765625</v>
       </c>
       <c r="D37" t="n">
-        <v>5737.02978515625</v>
+        <v>5724.31982421875</v>
       </c>
       <c r="E37" t="n">
-        <v>5830.18017578125</v>
+        <v>5758.77001953125</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -1188,19 +1188,19 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45887</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>5776.31005859375</v>
+        <v>5807.919921875</v>
       </c>
       <c r="C38" t="n">
-        <v>5781</v>
+        <v>5824.06982421875</v>
       </c>
       <c r="D38" t="n">
-        <v>5738.5498046875</v>
+        <v>5777.5498046875</v>
       </c>
       <c r="E38" t="n">
-        <v>5742.490234375</v>
+        <v>5780.14013671875</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1208,19 +1208,19 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45888</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>5671.509765625</v>
+        <v>5824.60986328125</v>
       </c>
       <c r="C39" t="n">
-        <v>5797.9599609375</v>
+        <v>5831.509765625</v>
       </c>
       <c r="D39" t="n">
-        <v>5664.93017578125</v>
+        <v>5766.77001953125</v>
       </c>
       <c r="E39" t="n">
-        <v>5777.66015625</v>
+        <v>5789.72021484375</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1228,19 +1228,19 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45889</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>5630.81982421875</v>
+        <v>5853.0498046875</v>
       </c>
       <c r="C40" t="n">
-        <v>5644.31005859375</v>
+        <v>5889.06005859375</v>
       </c>
       <c r="D40" t="n">
-        <v>5480.0498046875</v>
+        <v>5808.93994140625</v>
       </c>
       <c r="E40" t="n">
-        <v>5642.89990234375</v>
+        <v>5859.18017578125</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -1248,19 +1248,19 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45890</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>5603.259765625</v>
+        <v>5668.93994140625</v>
       </c>
       <c r="C41" t="n">
-        <v>5643.4501953125</v>
+        <v>5758.7001953125</v>
       </c>
       <c r="D41" t="n">
-        <v>5574.259765625</v>
+        <v>5646.169921875</v>
       </c>
       <c r="E41" t="n">
-        <v>5607.6201171875</v>
+        <v>5757.97021484375</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -1268,19 +1268,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45891</v>
+        <v>45902</v>
       </c>
       <c r="B42" t="n">
-        <v>5754.4599609375</v>
+        <v>5605.4599609375</v>
       </c>
       <c r="C42" t="n">
-        <v>5818.22998046875</v>
+        <v>5609.41015625</v>
       </c>
       <c r="D42" t="n">
-        <v>5598.8798828125</v>
+        <v>5503.1201171875</v>
       </c>
       <c r="E42" t="n">
-        <v>5612.31982421875</v>
+        <v>5509.41015625</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45894</v>
+        <v>45903</v>
       </c>
       <c r="B43" t="n">
-        <v>5756.2998046875</v>
+        <v>5592.81982421875</v>
       </c>
       <c r="C43" t="n">
-        <v>5784.60009765625</v>
+        <v>5624.759765625</v>
       </c>
       <c r="D43" t="n">
-        <v>5724.31982421875</v>
+        <v>5538.2001953125</v>
       </c>
       <c r="E43" t="n">
-        <v>5758.77001953125</v>
+        <v>5619.10009765625</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1308,19 +1308,19 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45895</v>
+        <v>45904</v>
       </c>
       <c r="B44" t="n">
-        <v>5807.919921875</v>
+        <v>5667.85986328125</v>
       </c>
       <c r="C44" t="n">
-        <v>5824.06982421875</v>
+        <v>5672.6201171875</v>
       </c>
       <c r="D44" t="n">
-        <v>5777.5498046875</v>
+        <v>5545.60009765625</v>
       </c>
       <c r="E44" t="n">
-        <v>5780.14013671875</v>
+        <v>5566.68994140625</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -1328,19 +1328,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="B45" t="n">
-        <v>5824.60986328125</v>
+        <v>5761.39990234375</v>
       </c>
       <c r="C45" t="n">
-        <v>5831.509765625</v>
+        <v>5792.97021484375</v>
       </c>
       <c r="D45" t="n">
-        <v>5766.77001953125</v>
+        <v>5687.14013671875</v>
       </c>
       <c r="E45" t="n">
-        <v>5789.72021484375</v>
+        <v>5775.41015625</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -1348,19 +1348,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45897</v>
+        <v>45908</v>
       </c>
       <c r="B46" t="n">
-        <v>5853.0498046875</v>
+        <v>5809.60986328125</v>
       </c>
       <c r="C46" t="n">
-        <v>5889.06005859375</v>
+        <v>5835.77001953125</v>
       </c>
       <c r="D46" t="n">
-        <v>5808.93994140625</v>
+        <v>5786.33984375</v>
       </c>
       <c r="E46" t="n">
-        <v>5859.18017578125</v>
+        <v>5804.02978515625</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1368,19 +1368,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45898</v>
+        <v>45909</v>
       </c>
       <c r="B47" t="n">
-        <v>5668.93994140625</v>
+        <v>5819.830078125</v>
       </c>
       <c r="C47" t="n">
-        <v>5758.7001953125</v>
+        <v>5830.16015625</v>
       </c>
       <c r="D47" t="n">
-        <v>5646.169921875</v>
+        <v>5776.009765625</v>
       </c>
       <c r="E47" t="n">
-        <v>5757.97021484375</v>
+        <v>5825.0400390625</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1388,19 +1388,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="B48" t="n">
-        <v>5605.4599609375</v>
+        <v>5958.08984375</v>
       </c>
       <c r="C48" t="n">
-        <v>5609.41015625</v>
+        <v>5977.60986328125</v>
       </c>
       <c r="D48" t="n">
-        <v>5503.1201171875</v>
+        <v>5911.509765625</v>
       </c>
       <c r="E48" t="n">
-        <v>5509.41015625</v>
+        <v>5921.9501953125</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1408,19 +1408,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="B49" t="n">
-        <v>5592.81982421875</v>
+        <v>5995.39013671875</v>
       </c>
       <c r="C49" t="n">
-        <v>5624.759765625</v>
+        <v>6033.52978515625</v>
       </c>
       <c r="D49" t="n">
-        <v>5538.2001953125</v>
+        <v>5987.52978515625</v>
       </c>
       <c r="E49" t="n">
-        <v>5619.10009765625</v>
+        <v>6008.39013671875</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1428,19 +1428,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="B50" t="n">
-        <v>5667.85986328125</v>
+        <v>6001.740234375</v>
       </c>
       <c r="C50" t="n">
-        <v>5672.6201171875</v>
+        <v>6021.759765625</v>
       </c>
       <c r="D50" t="n">
-        <v>5545.60009765625</v>
+        <v>5974.58984375</v>
       </c>
       <c r="E50" t="n">
-        <v>5566.68994140625</v>
+        <v>6018.3798828125</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="B51" t="n">
-        <v>5761.39990234375</v>
+        <v>6059.830078125</v>
       </c>
       <c r="C51" t="n">
-        <v>5792.97021484375</v>
+        <v>6062.2900390625</v>
       </c>
       <c r="D51" t="n">
-        <v>5687.14013671875</v>
+        <v>5979.990234375</v>
       </c>
       <c r="E51" t="n">
-        <v>5775.41015625</v>
+        <v>5993.8798828125</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -1468,19 +1468,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45908</v>
+        <v>45916</v>
       </c>
       <c r="B52" t="n">
-        <v>5809.60986328125</v>
+        <v>6079.22021484375</v>
       </c>
       <c r="C52" t="n">
-        <v>5835.77001953125</v>
+        <v>6098.1201171875</v>
       </c>
       <c r="D52" t="n">
-        <v>5786.33984375</v>
+        <v>6034.41015625</v>
       </c>
       <c r="E52" t="n">
-        <v>5804.02978515625</v>
+        <v>6085.97021484375</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -1488,19 +1488,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="B53" t="n">
-        <v>5819.830078125</v>
+        <v>6060.22021484375</v>
       </c>
       <c r="C53" t="n">
-        <v>5830.16015625</v>
+        <v>6109.080078125</v>
       </c>
       <c r="D53" t="n">
-        <v>5776.009765625</v>
+        <v>5980.240234375</v>
       </c>
       <c r="E53" t="n">
-        <v>5825.0400390625</v>
+        <v>6067.009765625</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1508,19 +1508,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45910</v>
+        <v>45918</v>
       </c>
       <c r="B54" t="n">
-        <v>5958.08984375</v>
+        <v>6278.16015625</v>
       </c>
       <c r="C54" t="n">
-        <v>5977.60986328125</v>
+        <v>6311.58984375</v>
       </c>
       <c r="D54" t="n">
-        <v>5911.509765625</v>
+        <v>6201.0498046875</v>
       </c>
       <c r="E54" t="n">
-        <v>5921.9501953125</v>
+        <v>6220.009765625</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -1528,19 +1528,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45911</v>
+        <v>45919</v>
       </c>
       <c r="B55" t="n">
-        <v>5995.39013671875</v>
+        <v>6232.25</v>
       </c>
       <c r="C55" t="n">
-        <v>6033.52978515625</v>
+        <v>6249.080078125</v>
       </c>
       <c r="D55" t="n">
-        <v>5987.52978515625</v>
+        <v>6184.66015625</v>
       </c>
       <c r="E55" t="n">
-        <v>6008.39013671875</v>
+        <v>6248.39013671875</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -1548,19 +1548,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45912</v>
+        <v>45922</v>
       </c>
       <c r="B56" t="n">
-        <v>6001.740234375</v>
+        <v>6330.1201171875</v>
       </c>
       <c r="C56" t="n">
-        <v>6021.759765625</v>
+        <v>6347.60009765625</v>
       </c>
       <c r="D56" t="n">
-        <v>5974.58984375</v>
+        <v>6246.7099609375</v>
       </c>
       <c r="E56" t="n">
-        <v>6018.3798828125</v>
+        <v>6247.830078125</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -1568,19 +1568,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="B57" t="n">
-        <v>6059.830078125</v>
+        <v>6308.2099609375</v>
       </c>
       <c r="C57" t="n">
-        <v>6062.2900390625</v>
+        <v>6374.6201171875</v>
       </c>
       <c r="D57" t="n">
-        <v>5979.990234375</v>
+        <v>6274.5400390625</v>
       </c>
       <c r="E57" t="n">
-        <v>5993.8798828125</v>
+        <v>6336.52978515625</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -1588,19 +1588,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45916</v>
+        <v>45924</v>
       </c>
       <c r="B58" t="n">
-        <v>6079.22021484375</v>
+        <v>6297</v>
       </c>
       <c r="C58" t="n">
-        <v>6098.1201171875</v>
+        <v>6313.919921875</v>
       </c>
       <c r="D58" t="n">
-        <v>6034.41015625</v>
+        <v>6216.3701171875</v>
       </c>
       <c r="E58" t="n">
-        <v>6085.97021484375</v>
+        <v>6282.18017578125</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -1608,19 +1608,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45917</v>
+        <v>45925</v>
       </c>
       <c r="B59" t="n">
-        <v>6060.22021484375</v>
+        <v>6284.669921875</v>
       </c>
       <c r="C59" t="n">
-        <v>6109.080078125</v>
+        <v>6298.7001953125</v>
       </c>
       <c r="D59" t="n">
-        <v>5980.240234375</v>
+        <v>6125.009765625</v>
       </c>
       <c r="E59" t="n">
-        <v>6067.009765625</v>
+        <v>6176.580078125</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -1628,19 +1628,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45918</v>
+        <v>45926</v>
       </c>
       <c r="B60" t="n">
-        <v>6278.16015625</v>
+        <v>6305.0498046875</v>
       </c>
       <c r="C60" t="n">
-        <v>6311.58984375</v>
+        <v>6313.0400390625</v>
       </c>
       <c r="D60" t="n">
-        <v>6201.0498046875</v>
+        <v>6229.72021484375</v>
       </c>
       <c r="E60" t="n">
-        <v>6220.009765625</v>
+        <v>6279.64013671875</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -1648,19 +1648,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="B61" t="n">
-        <v>6232.25</v>
+        <v>6315.10986328125</v>
       </c>
       <c r="C61" t="n">
-        <v>6249.080078125</v>
+        <v>6408.259765625</v>
       </c>
       <c r="D61" t="n">
-        <v>6184.66015625</v>
+        <v>6313.7099609375</v>
       </c>
       <c r="E61" t="n">
-        <v>6248.39013671875</v>
+        <v>6380.02001953125</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -1668,19 +1668,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45922</v>
+        <v>45930</v>
       </c>
       <c r="B62" t="n">
-        <v>6330.1201171875</v>
+        <v>6369.81982421875</v>
       </c>
       <c r="C62" t="n">
-        <v>6347.60009765625</v>
+        <v>6374.06005859375</v>
       </c>
       <c r="D62" t="n">
-        <v>6246.7099609375</v>
+        <v>6289.4501953125</v>
       </c>
       <c r="E62" t="n">
-        <v>6247.830078125</v>
+        <v>6322.56982421875</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -1688,19 +1688,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45923</v>
+        <v>45931</v>
       </c>
       <c r="B63" t="n">
-        <v>6308.2099609375</v>
+        <v>6500.27978515625</v>
       </c>
       <c r="C63" t="n">
-        <v>6374.6201171875</v>
+        <v>6507.02978515625</v>
       </c>
       <c r="D63" t="n">
-        <v>6274.5400390625</v>
+        <v>6317.7900390625</v>
       </c>
       <c r="E63" t="n">
-        <v>6336.52978515625</v>
+        <v>6321.7998046875</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -1708,19 +1708,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45924</v>
+        <v>45932</v>
       </c>
       <c r="B64" t="n">
-        <v>6297</v>
+        <v>6626.3798828125</v>
       </c>
       <c r="C64" t="n">
-        <v>6313.919921875</v>
+        <v>6643.7099609375</v>
       </c>
       <c r="D64" t="n">
-        <v>6216.3701171875</v>
+        <v>6573.10009765625</v>
       </c>
       <c r="E64" t="n">
-        <v>6282.18017578125</v>
+        <v>6633.3701171875</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -1728,19 +1728,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="B65" t="n">
-        <v>6284.669921875</v>
+        <v>6583.740234375</v>
       </c>
       <c r="C65" t="n">
-        <v>6298.7001953125</v>
+        <v>6683.43994140625</v>
       </c>
       <c r="D65" t="n">
-        <v>6125.009765625</v>
+        <v>6547.39990234375</v>
       </c>
       <c r="E65" t="n">
-        <v>6176.580078125</v>
+        <v>6655.06982421875</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -1748,19 +1748,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="B66" t="n">
-        <v>6305.0498046875</v>
+        <v>6774.06005859375</v>
       </c>
       <c r="C66" t="n">
-        <v>6313.0400390625</v>
+        <v>6881.91015625</v>
       </c>
       <c r="D66" t="n">
-        <v>6229.72021484375</v>
+        <v>6773.259765625</v>
       </c>
       <c r="E66" t="n">
-        <v>6279.64013671875</v>
+        <v>6852.72021484375</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -1768,19 +1768,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45929</v>
+        <v>45937</v>
       </c>
       <c r="B67" t="n">
-        <v>6315.10986328125</v>
+        <v>6634.759765625</v>
       </c>
       <c r="C67" t="n">
-        <v>6408.259765625</v>
+        <v>6847.509765625</v>
       </c>
       <c r="D67" t="n">
-        <v>6313.7099609375</v>
+        <v>6622.6298828125</v>
       </c>
       <c r="E67" t="n">
-        <v>6380.02001953125</v>
+        <v>6837.669921875</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -1788,19 +1788,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45930</v>
+        <v>45938</v>
       </c>
       <c r="B68" t="n">
-        <v>6369.81982421875</v>
+        <v>6860.2001953125</v>
       </c>
       <c r="C68" t="n">
-        <v>6374.06005859375</v>
+        <v>6867.08984375</v>
       </c>
       <c r="D68" t="n">
-        <v>6289.4501953125</v>
+        <v>6624.06982421875</v>
       </c>
       <c r="E68" t="n">
-        <v>6322.56982421875</v>
+        <v>6625.2900390625</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -1808,19 +1808,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45931</v>
+        <v>45939</v>
       </c>
       <c r="B69" t="n">
-        <v>6500.27978515625</v>
+        <v>6840.2001953125</v>
       </c>
       <c r="C69" t="n">
-        <v>6507.02978515625</v>
+        <v>6869.080078125</v>
       </c>
       <c r="D69" t="n">
-        <v>6317.7900390625</v>
+        <v>6776.830078125</v>
       </c>
       <c r="E69" t="n">
-        <v>6321.7998046875</v>
+        <v>6845.39013671875</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -1828,19 +1828,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45932</v>
+        <v>45940</v>
       </c>
       <c r="B70" t="n">
-        <v>6626.3798828125</v>
+        <v>6407.60009765625</v>
       </c>
       <c r="C70" t="n">
-        <v>6643.7099609375</v>
+        <v>6867.85986328125</v>
       </c>
       <c r="D70" t="n">
-        <v>6573.10009765625</v>
+        <v>6403.240234375</v>
       </c>
       <c r="E70" t="n">
-        <v>6633.3701171875</v>
+        <v>6853.43017578125</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -1848,19 +1848,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45933</v>
+        <v>45943</v>
       </c>
       <c r="B71" t="n">
-        <v>6583.740234375</v>
+        <v>6723.47021484375</v>
       </c>
       <c r="C71" t="n">
-        <v>6683.43994140625</v>
+        <v>6742.3701171875</v>
       </c>
       <c r="D71" t="n">
-        <v>6547.39990234375</v>
+        <v>6612.8798828125</v>
       </c>
       <c r="E71" t="n">
-        <v>6655.06982421875</v>
+        <v>6662.89013671875</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -1868,19 +1868,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45936</v>
+        <v>45944</v>
       </c>
       <c r="B72" t="n">
-        <v>6774.06005859375</v>
+        <v>6570.330078125</v>
       </c>
       <c r="C72" t="n">
-        <v>6881.91015625</v>
+        <v>6706.4501953125</v>
       </c>
       <c r="D72" t="n">
-        <v>6773.259765625</v>
+        <v>6532.740234375</v>
       </c>
       <c r="E72" t="n">
-        <v>6852.72021484375</v>
+        <v>6582.330078125</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -1888,19 +1888,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45937</v>
+        <v>45945</v>
       </c>
       <c r="B73" t="n">
-        <v>6634.759765625</v>
+        <v>6767.06005859375</v>
       </c>
       <c r="C73" t="n">
-        <v>6847.509765625</v>
+        <v>6780.72998046875</v>
       </c>
       <c r="D73" t="n">
-        <v>6622.6298828125</v>
+        <v>6632.14013671875</v>
       </c>
       <c r="E73" t="n">
-        <v>6837.669921875</v>
+        <v>6723.009765625</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -1908,19 +1908,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45938</v>
+        <v>45946</v>
       </c>
       <c r="B74" t="n">
-        <v>6860.2001953125</v>
+        <v>6800.02001953125</v>
       </c>
       <c r="C74" t="n">
-        <v>6867.08984375</v>
+        <v>6880.56982421875</v>
       </c>
       <c r="D74" t="n">
-        <v>6624.06982421875</v>
+        <v>6727.9599609375</v>
       </c>
       <c r="E74" t="n">
-        <v>6625.2900390625</v>
+        <v>6848.22021484375</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -1928,19 +1928,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45939</v>
+        <v>45947</v>
       </c>
       <c r="B75" t="n">
-        <v>6840.2001953125</v>
+        <v>6777.97998046875</v>
       </c>
       <c r="C75" t="n">
-        <v>6869.080078125</v>
+        <v>6812.27978515625</v>
       </c>
       <c r="D75" t="n">
-        <v>6776.830078125</v>
+        <v>6673.580078125</v>
       </c>
       <c r="E75" t="n">
-        <v>6845.39013671875</v>
+        <v>6742.02978515625</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -1948,19 +1948,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
       <c r="B76" t="n">
-        <v>6407.60009765625</v>
+        <v>6885.02978515625</v>
       </c>
       <c r="C76" t="n">
-        <v>6867.85986328125</v>
+        <v>6935.64990234375</v>
       </c>
       <c r="D76" t="n">
-        <v>6403.240234375</v>
+        <v>6855.18017578125</v>
       </c>
       <c r="E76" t="n">
-        <v>6853.43017578125</v>
+        <v>6858.6298828125</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -1968,19 +1968,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45943</v>
+        <v>45951</v>
       </c>
       <c r="B77" t="n">
-        <v>6723.47021484375</v>
+        <v>6839.27001953125</v>
       </c>
       <c r="C77" t="n">
-        <v>6742.3701171875</v>
+        <v>6875.72998046875</v>
       </c>
       <c r="D77" t="n">
-        <v>6612.8798828125</v>
+        <v>6793.1201171875</v>
       </c>
       <c r="E77" t="n">
-        <v>6662.89013671875</v>
+        <v>6864.240234375</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -1988,19 +1988,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45944</v>
+        <v>45952</v>
       </c>
       <c r="B78" t="n">
-        <v>6570.330078125</v>
+        <v>6677.56982421875</v>
       </c>
       <c r="C78" t="n">
-        <v>6706.4501953125</v>
+        <v>6819.83984375</v>
       </c>
       <c r="D78" t="n">
-        <v>6532.740234375</v>
+        <v>6547.3701171875</v>
       </c>
       <c r="E78" t="n">
-        <v>6582.330078125</v>
+        <v>6764.43994140625</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -2008,19 +2008,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45945</v>
+        <v>45953</v>
       </c>
       <c r="B79" t="n">
-        <v>6767.06005859375</v>
+        <v>6847.39013671875</v>
       </c>
       <c r="C79" t="n">
-        <v>6780.72998046875</v>
+        <v>6861.4599609375</v>
       </c>
       <c r="D79" t="n">
-        <v>6632.14013671875</v>
+        <v>6648.330078125</v>
       </c>
       <c r="E79" t="n">
-        <v>6723.009765625</v>
+        <v>6648.330078125</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -2028,19 +2028,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45946</v>
+        <v>45954</v>
       </c>
       <c r="B80" t="n">
-        <v>6800.02001953125</v>
+        <v>6976.93994140625</v>
       </c>
       <c r="C80" t="n">
-        <v>6880.56982421875</v>
+        <v>7021.3798828125</v>
       </c>
       <c r="D80" t="n">
-        <v>6727.9599609375</v>
+        <v>6961.16015625</v>
       </c>
       <c r="E80" t="n">
-        <v>6848.22021484375</v>
+        <v>6970.16015625</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -2048,19 +2048,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45947</v>
+        <v>45957</v>
       </c>
       <c r="B81" t="n">
-        <v>6777.97998046875</v>
+        <v>7167.97998046875</v>
       </c>
       <c r="C81" t="n">
-        <v>6812.27978515625</v>
+        <v>7175.52978515625</v>
       </c>
       <c r="D81" t="n">
-        <v>6673.580078125</v>
+        <v>7083.10009765625</v>
       </c>
       <c r="E81" t="n">
-        <v>6742.02978515625</v>
+        <v>7103.56005859375</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -2068,19 +2068,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45950</v>
+        <v>45958</v>
       </c>
       <c r="B82" t="n">
-        <v>6885.02978515625</v>
+        <v>7194.7099609375</v>
       </c>
       <c r="C82" t="n">
-        <v>6935.64990234375</v>
+        <v>7223.77001953125</v>
       </c>
       <c r="D82" t="n">
-        <v>6855.18017578125</v>
+        <v>7136.3798828125</v>
       </c>
       <c r="E82" t="n">
-        <v>6858.6298828125</v>
+        <v>7158.16015625</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -2088,19 +2088,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45951</v>
+        <v>45959</v>
       </c>
       <c r="B83" t="n">
-        <v>6839.27001953125</v>
+        <v>7327.93017578125</v>
       </c>
       <c r="C83" t="n">
-        <v>6875.72998046875</v>
+        <v>7392.64013671875</v>
       </c>
       <c r="D83" t="n">
-        <v>6793.1201171875</v>
+        <v>7257.81982421875</v>
       </c>
       <c r="E83" t="n">
-        <v>6864.240234375</v>
+        <v>7342.5400390625</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -2108,19 +2108,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="B84" t="n">
-        <v>6677.56982421875</v>
+        <v>7216</v>
       </c>
       <c r="C84" t="n">
-        <v>6819.83984375</v>
+        <v>7351.0498046875</v>
       </c>
       <c r="D84" t="n">
-        <v>6547.3701171875</v>
+        <v>7213.39990234375</v>
       </c>
       <c r="E84" t="n">
-        <v>6764.43994140625</v>
+        <v>7283.08984375</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -2128,19 +2128,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45953</v>
+        <v>45961</v>
       </c>
       <c r="B85" t="n">
-        <v>6847.39013671875</v>
+        <v>7228.66015625</v>
       </c>
       <c r="C85" t="n">
-        <v>6861.4599609375</v>
+        <v>7345.91015625</v>
       </c>
       <c r="D85" t="n">
-        <v>6648.330078125</v>
+        <v>7171.740234375</v>
       </c>
       <c r="E85" t="n">
-        <v>6648.330078125</v>
+        <v>7284.330078125</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -2148,19 +2148,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45954</v>
+        <v>45964</v>
       </c>
       <c r="B86" t="n">
-        <v>6976.93994140625</v>
+        <v>7270.97021484375</v>
       </c>
       <c r="C86" t="n">
-        <v>7021.3798828125</v>
+        <v>7353.6298828125</v>
       </c>
       <c r="D86" t="n">
-        <v>6961.16015625</v>
+        <v>7248.68994140625</v>
       </c>
       <c r="E86" t="n">
-        <v>6970.16015625</v>
+        <v>7342.7998046875</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -2168,19 +2168,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="B87" t="n">
-        <v>7167.97998046875</v>
+        <v>6979.56982421875</v>
       </c>
       <c r="C87" t="n">
-        <v>7175.52978515625</v>
+        <v>7190.58984375</v>
       </c>
       <c r="D87" t="n">
-        <v>7083.10009765625</v>
+        <v>6972.3701171875</v>
       </c>
       <c r="E87" t="n">
-        <v>7103.56005859375</v>
+        <v>7074.4501953125</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -2188,19 +2188,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45958</v>
+        <v>45966</v>
       </c>
       <c r="B88" t="n">
-        <v>7194.7099609375</v>
+        <v>7190.27001953125</v>
       </c>
       <c r="C88" t="n">
-        <v>7223.77001953125</v>
+        <v>7277.81982421875</v>
       </c>
       <c r="D88" t="n">
-        <v>7136.3798828125</v>
+        <v>7022.9501953125</v>
       </c>
       <c r="E88" t="n">
-        <v>7158.16015625</v>
+        <v>7024.27978515625</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -2208,19 +2208,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45959</v>
+        <v>45967</v>
       </c>
       <c r="B89" t="n">
-        <v>7327.93017578125</v>
+        <v>7018.39013671875</v>
       </c>
       <c r="C89" t="n">
-        <v>7392.64013671875</v>
+        <v>7226.06005859375</v>
       </c>
       <c r="D89" t="n">
-        <v>7257.81982421875</v>
+        <v>6974.1201171875</v>
       </c>
       <c r="E89" t="n">
-        <v>7342.5400390625</v>
+        <v>7195.22998046875</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -2228,19 +2228,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45960</v>
+        <v>45968</v>
       </c>
       <c r="B90" t="n">
-        <v>7216</v>
+        <v>6947.35986328125</v>
       </c>
       <c r="C90" t="n">
-        <v>7351.0498046875</v>
+        <v>6949.14990234375</v>
       </c>
       <c r="D90" t="n">
-        <v>7213.39990234375</v>
+        <v>6688.83984375</v>
       </c>
       <c r="E90" t="n">
-        <v>7283.08984375</v>
+        <v>6917.75</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -2248,19 +2248,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="B91" t="n">
-        <v>7228.66015625</v>
+        <v>7156.9501953125</v>
       </c>
       <c r="C91" t="n">
-        <v>7345.91015625</v>
+        <v>7178.35009765625</v>
       </c>
       <c r="D91" t="n">
-        <v>7171.740234375</v>
+        <v>7066.47998046875</v>
       </c>
       <c r="E91" t="n">
-        <v>7284.330078125</v>
+        <v>7136.66015625</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -2268,19 +2268,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="B92" t="n">
-        <v>7270.97021484375</v>
+        <v>6979.7001953125</v>
       </c>
       <c r="C92" t="n">
-        <v>7353.6298828125</v>
+        <v>7099.81005859375</v>
       </c>
       <c r="D92" t="n">
-        <v>7248.68994140625</v>
+        <v>6965.759765625</v>
       </c>
       <c r="E92" t="n">
-        <v>7342.7998046875</v>
+        <v>7077.3798828125</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -2288,19 +2288,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45965</v>
+        <v>45973</v>
       </c>
       <c r="B93" t="n">
-        <v>6979.56982421875</v>
+        <v>7082.1298828125</v>
       </c>
       <c r="C93" t="n">
-        <v>7190.58984375</v>
+        <v>7130.5498046875</v>
       </c>
       <c r="D93" t="n">
-        <v>6972.3701171875</v>
+        <v>7035.27001953125</v>
       </c>
       <c r="E93" t="n">
-        <v>7074.4501953125</v>
+        <v>7112.16015625</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -2308,19 +2308,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45966</v>
+        <v>45974</v>
       </c>
       <c r="B94" t="n">
-        <v>7190.27001953125</v>
+        <v>6818.740234375</v>
       </c>
       <c r="C94" t="n">
-        <v>7277.81982421875</v>
+        <v>7008.43994140625</v>
       </c>
       <c r="D94" t="n">
-        <v>7022.9501953125</v>
+        <v>6750.1201171875</v>
       </c>
       <c r="E94" t="n">
-        <v>7024.27978515625</v>
+        <v>7003.169921875</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -2328,19 +2328,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45967</v>
+        <v>45975</v>
       </c>
       <c r="B95" t="n">
-        <v>7018.39013671875</v>
+        <v>6811.2001953125</v>
       </c>
       <c r="C95" t="n">
-        <v>7226.06005859375</v>
+        <v>6911.919921875</v>
       </c>
       <c r="D95" t="n">
-        <v>6974.1201171875</v>
+        <v>6587.83984375</v>
       </c>
       <c r="E95" t="n">
-        <v>7195.22998046875</v>
+        <v>6634.93994140625</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -2348,19 +2348,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45968</v>
+        <v>45978</v>
       </c>
       <c r="B96" t="n">
-        <v>6947.35986328125</v>
+        <v>6705.740234375</v>
       </c>
       <c r="C96" t="n">
-        <v>6949.14990234375</v>
+        <v>6886.6298828125</v>
       </c>
       <c r="D96" t="n">
-        <v>6688.83984375</v>
+        <v>6631.31982421875</v>
       </c>
       <c r="E96" t="n">
-        <v>6917.75</v>
+        <v>6756.56005859375</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -2368,19 +2368,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45971</v>
+        <v>45979</v>
       </c>
       <c r="B97" t="n">
-        <v>7156.9501953125</v>
+        <v>6551.02978515625</v>
       </c>
       <c r="C97" t="n">
-        <v>7178.35009765625</v>
+        <v>6651.58984375</v>
       </c>
       <c r="D97" t="n">
-        <v>7066.47998046875</v>
+        <v>6479.68017578125</v>
       </c>
       <c r="E97" t="n">
-        <v>7136.66015625</v>
+        <v>6622.009765625</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -2388,19 +2388,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45972</v>
+        <v>45980</v>
       </c>
       <c r="B98" t="n">
-        <v>6979.7001953125</v>
+        <v>6670.02978515625</v>
       </c>
       <c r="C98" t="n">
-        <v>7099.81005859375</v>
+        <v>6751.81982421875</v>
       </c>
       <c r="D98" t="n">
-        <v>6965.759765625</v>
+        <v>6552.97021484375</v>
       </c>
       <c r="E98" t="n">
-        <v>7077.3798828125</v>
+        <v>6577.27978515625</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -2408,19 +2408,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B99" t="n">
-        <v>7082.1298828125</v>
+        <v>6352.06982421875</v>
       </c>
       <c r="C99" t="n">
-        <v>7130.5498046875</v>
+        <v>6882.990234375</v>
       </c>
       <c r="D99" t="n">
-        <v>7035.27001953125</v>
+        <v>6327.7900390625</v>
       </c>
       <c r="E99" t="n">
-        <v>7112.16015625</v>
+        <v>6863.1201171875</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -2428,19 +2428,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45974</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>6818.740234375</v>
+        <v>6406.43017578125</v>
       </c>
       <c r="C100" t="n">
-        <v>7008.43994140625</v>
+        <v>6505.8798828125</v>
       </c>
       <c r="D100" t="n">
-        <v>6750.1201171875</v>
+        <v>6160.0498046875</v>
       </c>
       <c r="E100" t="n">
-        <v>7003.169921875</v>
+        <v>6351.0498046875</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -2448,19 +2448,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45975</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>6811.2001953125</v>
+        <v>6703.2001953125</v>
       </c>
       <c r="C101" t="n">
-        <v>6911.919921875</v>
+        <v>6733.02978515625</v>
       </c>
       <c r="D101" t="n">
-        <v>6587.83984375</v>
+        <v>6475.39013671875</v>
       </c>
       <c r="E101" t="n">
-        <v>6634.93994140625</v>
+        <v>6494.85986328125</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -2468,19 +2468,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>6705.740234375</v>
+        <v>6714.18017578125</v>
       </c>
       <c r="C102" t="n">
-        <v>6886.6298828125</v>
+        <v>6730.9599609375</v>
       </c>
       <c r="D102" t="n">
-        <v>6631.31982421875</v>
+        <v>6457.2998046875</v>
       </c>
       <c r="E102" t="n">
-        <v>6756.56005859375</v>
+        <v>6617.14013671875</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -2488,19 +2488,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>6551.02978515625</v>
+        <v>6899.4599609375</v>
       </c>
       <c r="C103" t="n">
-        <v>6651.58984375</v>
+        <v>6958.93017578125</v>
       </c>
       <c r="D103" t="n">
-        <v>6479.68017578125</v>
+        <v>6790.27978515625</v>
       </c>
       <c r="E103" t="n">
-        <v>6622.009765625</v>
+        <v>6801.5498046875</v>
       </c>
       <c r="F103" t="n">
         <v>0</v>
@@ -2508,19 +2508,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="B104" t="n">
-        <v>6670.02978515625</v>
+        <v>7025.14990234375</v>
       </c>
       <c r="C104" t="n">
-        <v>6751.81982421875</v>
+        <v>7028.14013671875</v>
       </c>
       <c r="D104" t="n">
-        <v>6552.97021484375</v>
+        <v>6907.7998046875</v>
       </c>
       <c r="E104" t="n">
-        <v>6577.27978515625</v>
+        <v>6926.91015625</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -2528,19 +2528,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45981</v>
+        <v>45992</v>
       </c>
       <c r="B105" t="n">
-        <v>6352.06982421875</v>
+        <v>7020.52978515625</v>
       </c>
       <c r="C105" t="n">
-        <v>6882.990234375</v>
+        <v>7081.1201171875</v>
       </c>
       <c r="D105" t="n">
-        <v>6327.7900390625</v>
+        <v>6920.669921875</v>
       </c>
       <c r="E105" t="n">
-        <v>6863.1201171875</v>
+        <v>6945.2001953125</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -2548,19 +2548,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45982</v>
+        <v>45993</v>
       </c>
       <c r="B106" t="n">
-        <v>6406.43017578125</v>
+        <v>7149.47021484375</v>
       </c>
       <c r="C106" t="n">
-        <v>6505.8798828125</v>
+        <v>7211.14013671875</v>
       </c>
       <c r="D106" t="n">
-        <v>6160.0498046875</v>
+        <v>7057.31005859375</v>
       </c>
       <c r="E106" t="n">
-        <v>6351.0498046875</v>
+        <v>7098.60986328125</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -2568,19 +2568,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45985</v>
+        <v>45994</v>
       </c>
       <c r="B107" t="n">
-        <v>6703.2001953125</v>
+        <v>7280.509765625</v>
       </c>
       <c r="C107" t="n">
-        <v>6733.02978515625</v>
+        <v>7284.35986328125</v>
       </c>
       <c r="D107" t="n">
-        <v>6475.39013671875</v>
+        <v>7099.81005859375</v>
       </c>
       <c r="E107" t="n">
-        <v>6494.85986328125</v>
+        <v>7164.81982421875</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
@@ -2588,19 +2588,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="B108" t="n">
-        <v>6714.18017578125</v>
+        <v>7215.97021484375</v>
       </c>
       <c r="C108" t="n">
-        <v>6730.9599609375</v>
+        <v>7267.35986328125</v>
       </c>
       <c r="D108" t="n">
-        <v>6457.2998046875</v>
+        <v>7180.77978515625</v>
       </c>
       <c r="E108" t="n">
-        <v>6617.14013671875</v>
+        <v>7238.72998046875</v>
       </c>
       <c r="F108" t="n">
         <v>0</v>
@@ -2608,19 +2608,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45987</v>
+        <v>45996</v>
       </c>
       <c r="B109" t="n">
-        <v>6899.4599609375</v>
+        <v>7294.83984375</v>
       </c>
       <c r="C109" t="n">
-        <v>6958.93017578125</v>
+        <v>7377.2998046875</v>
       </c>
       <c r="D109" t="n">
-        <v>6790.27978515625</v>
+        <v>7282.2900390625</v>
       </c>
       <c r="E109" t="n">
-        <v>6801.5498046875</v>
+        <v>7303.06005859375</v>
       </c>
       <c r="F109" t="n">
         <v>0</v>
@@ -2628,19 +2628,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45989</v>
+        <v>45999</v>
       </c>
       <c r="B110" t="n">
-        <v>7025.14990234375</v>
+        <v>7375.22021484375</v>
       </c>
       <c r="C110" t="n">
-        <v>7028.14013671875</v>
+        <v>7410.5</v>
       </c>
       <c r="D110" t="n">
-        <v>6907.7998046875</v>
+        <v>7302.7001953125</v>
       </c>
       <c r="E110" t="n">
-        <v>6926.91015625</v>
+        <v>7358.16015625</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -2648,19 +2648,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="B111" t="n">
-        <v>7020.52978515625</v>
+        <v>7372.509765625</v>
       </c>
       <c r="C111" t="n">
-        <v>7081.1201171875</v>
+        <v>7386.4501953125</v>
       </c>
       <c r="D111" t="n">
-        <v>6920.669921875</v>
+        <v>7299.9599609375</v>
       </c>
       <c r="E111" t="n">
-        <v>6945.2001953125</v>
+        <v>7325.830078125</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -2668,19 +2668,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="B112" t="n">
-        <v>7149.47021484375</v>
+        <v>7467.490234375</v>
       </c>
       <c r="C112" t="n">
-        <v>7211.14013671875</v>
+        <v>7490.27978515625</v>
       </c>
       <c r="D112" t="n">
-        <v>7057.31005859375</v>
+        <v>7333.4599609375</v>
       </c>
       <c r="E112" t="n">
-        <v>7098.60986328125</v>
+        <v>7369.72998046875</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="B113" t="n">
-        <v>7280.509765625</v>
+        <v>7411.47998046875</v>
       </c>
       <c r="C113" t="n">
-        <v>7284.35986328125</v>
+        <v>7419.6201171875</v>
       </c>
       <c r="D113" t="n">
-        <v>7099.81005859375</v>
+        <v>7208.22998046875</v>
       </c>
       <c r="E113" t="n">
-        <v>7164.81982421875</v>
+        <v>7353.080078125</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -2708,19 +2708,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45995</v>
+        <v>46003</v>
       </c>
       <c r="B114" t="n">
-        <v>7215.97021484375</v>
+        <v>7033.56982421875</v>
       </c>
       <c r="C114" t="n">
-        <v>7267.35986328125</v>
+        <v>7331.3798828125</v>
       </c>
       <c r="D114" t="n">
-        <v>7180.77978515625</v>
+        <v>7003.39990234375</v>
       </c>
       <c r="E114" t="n">
-        <v>7238.72998046875</v>
+        <v>7297.85009765625</v>
       </c>
       <c r="F114" t="n">
         <v>0</v>
@@ -2728,19 +2728,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45996</v>
+        <v>46006</v>
       </c>
       <c r="B115" t="n">
-        <v>7294.83984375</v>
+        <v>6990.41015625</v>
       </c>
       <c r="C115" t="n">
-        <v>7377.2998046875</v>
+        <v>7125.9599609375</v>
       </c>
       <c r="D115" t="n">
-        <v>7282.2900390625</v>
+        <v>6971.39990234375</v>
       </c>
       <c r="E115" t="n">
-        <v>7303.06005859375</v>
+        <v>7096.27001953125</v>
       </c>
       <c r="F115" t="n">
         <v>0</v>
@@ -2748,19 +2748,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45999</v>
+        <v>46007</v>
       </c>
       <c r="B116" t="n">
-        <v>7375.22021484375</v>
+        <v>6958.43994140625</v>
       </c>
       <c r="C116" t="n">
-        <v>7410.5</v>
+        <v>7019.10986328125</v>
       </c>
       <c r="D116" t="n">
-        <v>7302.7001953125</v>
+        <v>6888.6201171875</v>
       </c>
       <c r="E116" t="n">
-        <v>7358.16015625</v>
+        <v>6977.89990234375</v>
       </c>
       <c r="F116" t="n">
         <v>0</v>
@@ -2768,19 +2768,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="B117" t="n">
-        <v>7372.509765625</v>
+        <v>6695.31005859375</v>
       </c>
       <c r="C117" t="n">
-        <v>7386.4501953125</v>
+        <v>7005.080078125</v>
       </c>
       <c r="D117" t="n">
-        <v>7299.9599609375</v>
+        <v>6680.68017578125</v>
       </c>
       <c r="E117" t="n">
-        <v>7325.830078125</v>
+        <v>6993.10009765625</v>
       </c>
       <c r="F117" t="n">
         <v>0</v>
@@ -2788,19 +2788,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="B118" t="n">
-        <v>7467.490234375</v>
+        <v>6863.6298828125</v>
       </c>
       <c r="C118" t="n">
-        <v>7490.27978515625</v>
+        <v>6970.18994140625</v>
       </c>
       <c r="D118" t="n">
-        <v>7333.4599609375</v>
+        <v>6831.72998046875</v>
       </c>
       <c r="E118" t="n">
-        <v>7369.72998046875</v>
+        <v>6938.919921875</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -2808,19 +2808,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="B119" t="n">
-        <v>7411.47998046875</v>
+        <v>7067.8701171875</v>
       </c>
       <c r="C119" t="n">
-        <v>7419.6201171875</v>
+        <v>7095.009765625</v>
       </c>
       <c r="D119" t="n">
-        <v>7208.22998046875</v>
+        <v>6942.4599609375</v>
       </c>
       <c r="E119" t="n">
-        <v>7353.080078125</v>
+        <v>6942.4599609375</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -2828,19 +2828,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46003</v>
+        <v>46013</v>
       </c>
       <c r="B120" t="n">
-        <v>7033.56982421875</v>
+        <v>7145.56982421875</v>
       </c>
       <c r="C120" t="n">
-        <v>7331.3798828125</v>
+        <v>7206.39013671875</v>
       </c>
       <c r="D120" t="n">
-        <v>7003.39990234375</v>
+        <v>7120.0400390625</v>
       </c>
       <c r="E120" t="n">
-        <v>7297.85009765625</v>
+        <v>7204.02001953125</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -2848,19 +2848,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="B121" t="n">
-        <v>6990.41015625</v>
+        <v>7184.5400390625</v>
       </c>
       <c r="C121" t="n">
-        <v>7125.9599609375</v>
+        <v>7186.39013671875</v>
       </c>
       <c r="D121" t="n">
-        <v>6971.39990234375</v>
+        <v>7091.4599609375</v>
       </c>
       <c r="E121" t="n">
-        <v>7096.27001953125</v>
+        <v>7118.39013671875</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -2868,19 +2868,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46007</v>
+        <v>46015</v>
       </c>
       <c r="B122" t="n">
-        <v>6958.43994140625</v>
+        <v>7204.3701171875</v>
       </c>
       <c r="C122" t="n">
-        <v>7019.10986328125</v>
+        <v>7212.5498046875</v>
       </c>
       <c r="D122" t="n">
-        <v>6888.6201171875</v>
+        <v>7173.27001953125</v>
       </c>
       <c r="E122" t="n">
-        <v>6977.89990234375</v>
+        <v>7191.72021484375</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -2888,19 +2888,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46008</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>6695.31005859375</v>
+        <v>7207.64013671875</v>
       </c>
       <c r="C123" t="n">
-        <v>7005.080078125</v>
+        <v>7233.06005859375</v>
       </c>
       <c r="D123" t="n">
-        <v>6680.68017578125</v>
+        <v>7188.580078125</v>
       </c>
       <c r="E123" t="n">
-        <v>6993.10009765625</v>
+        <v>7229.66015625</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -2908,19 +2908,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46009</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>6863.6298828125</v>
+        <v>7178.27001953125</v>
       </c>
       <c r="C124" t="n">
-        <v>6970.18994140625</v>
+        <v>7205.22021484375</v>
       </c>
       <c r="D124" t="n">
-        <v>6831.72998046875</v>
+        <v>7098.77001953125</v>
       </c>
       <c r="E124" t="n">
-        <v>6938.919921875</v>
+        <v>7116.14990234375</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -2928,19 +2928,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46010</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>7067.8701171875</v>
+        <v>7169.10009765625</v>
       </c>
       <c r="C125" t="n">
-        <v>7095.009765625</v>
+        <v>7229.759765625</v>
       </c>
       <c r="D125" t="n">
-        <v>6942.4599609375</v>
+        <v>7167.02001953125</v>
       </c>
       <c r="E125" t="n">
-        <v>6942.4599609375</v>
+        <v>7206.0498046875</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -2948,19 +2948,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="B126" t="n">
-        <v>7145.56982421875</v>
+        <v>7083.1298828125</v>
       </c>
       <c r="C126" t="n">
-        <v>7206.39013671875</v>
+        <v>7193.5</v>
       </c>
       <c r="D126" t="n">
-        <v>7120.0400390625</v>
+        <v>7082.64990234375</v>
       </c>
       <c r="E126" t="n">
-        <v>7204.02001953125</v>
+        <v>7184.85009765625</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -2968,19 +2968,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46014</v>
+        <v>46024</v>
       </c>
       <c r="B127" t="n">
-        <v>7184.5400390625</v>
+        <v>7367.47021484375</v>
       </c>
       <c r="C127" t="n">
-        <v>7186.39013671875</v>
+        <v>7418.25</v>
       </c>
       <c r="D127" t="n">
-        <v>7091.4599609375</v>
+        <v>7286.33984375</v>
       </c>
       <c r="E127" t="n">
-        <v>7118.39013671875</v>
+        <v>7288.669921875</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -2988,19 +2988,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46015</v>
+        <v>46027</v>
       </c>
       <c r="B128" t="n">
-        <v>7204.3701171875</v>
+        <v>7446.4501953125</v>
       </c>
       <c r="C128" t="n">
-        <v>7212.5498046875</v>
+        <v>7577.27978515625</v>
       </c>
       <c r="D128" t="n">
-        <v>7173.27001953125</v>
+        <v>7415.7001953125</v>
       </c>
       <c r="E128" t="n">
-        <v>7191.72021484375</v>
+        <v>7570.43994140625</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -3008,19 +3008,19 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46017</v>
+        <v>46028</v>
       </c>
       <c r="B129" t="n">
-        <v>7207.64013671875</v>
+        <v>7650.93017578125</v>
       </c>
       <c r="C129" t="n">
-        <v>7233.06005859375</v>
+        <v>7665.77001953125</v>
       </c>
       <c r="D129" t="n">
-        <v>7188.580078125</v>
+        <v>7521.9501953125</v>
       </c>
       <c r="E129" t="n">
-        <v>7229.66015625</v>
+        <v>7542.60986328125</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -3028,19 +3028,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46020</v>
+        <v>46029</v>
       </c>
       <c r="B130" t="n">
-        <v>7178.27001953125</v>
+        <v>7574.8701171875</v>
       </c>
       <c r="C130" t="n">
-        <v>7205.22021484375</v>
+        <v>7601.06005859375</v>
       </c>
       <c r="D130" t="n">
-        <v>7098.77001953125</v>
+        <v>7512.85986328125</v>
       </c>
       <c r="E130" t="n">
-        <v>7116.14990234375</v>
+        <v>7554.77978515625</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -3048,19 +3048,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46021</v>
+        <v>46030</v>
       </c>
       <c r="B131" t="n">
-        <v>7169.10009765625</v>
+        <v>7436.10009765625</v>
       </c>
       <c r="C131" t="n">
-        <v>7229.759765625</v>
+        <v>7548.31005859375</v>
       </c>
       <c r="D131" t="n">
-        <v>7167.02001953125</v>
+        <v>7372.7900390625</v>
       </c>
       <c r="E131" t="n">
-        <v>7206.0498046875</v>
+        <v>7543.25</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -3068,19 +3068,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="B132" t="n">
-        <v>7083.1298828125</v>
+        <v>7638.77978515625</v>
       </c>
       <c r="C132" t="n">
-        <v>7193.5</v>
+        <v>7678.89013671875</v>
       </c>
       <c r="D132" t="n">
-        <v>7082.64990234375</v>
+        <v>7467.830078125</v>
       </c>
       <c r="E132" t="n">
-        <v>7184.85009765625</v>
+        <v>7471.330078125</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -3088,19 +3088,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="B133" t="n">
-        <v>7367.47021484375</v>
+        <v>7674.83984375</v>
       </c>
       <c r="C133" t="n">
-        <v>7418.25</v>
+        <v>7703.14013671875</v>
       </c>
       <c r="D133" t="n">
-        <v>7286.33984375</v>
+        <v>7568.06982421875</v>
       </c>
       <c r="E133" t="n">
-        <v>7288.669921875</v>
+        <v>7574.240234375</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -3108,19 +3108,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46027</v>
+        <v>46035</v>
       </c>
       <c r="B134" t="n">
-        <v>7446.4501953125</v>
+        <v>7747.990234375</v>
       </c>
       <c r="C134" t="n">
-        <v>7577.27978515625</v>
+        <v>7825.8798828125</v>
       </c>
       <c r="D134" t="n">
-        <v>7415.7001953125</v>
+        <v>7715.8798828125</v>
       </c>
       <c r="E134" t="n">
-        <v>7570.43994140625</v>
+        <v>7725.080078125</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -3128,19 +3128,19 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46028</v>
+        <v>46036</v>
       </c>
       <c r="B135" t="n">
-        <v>7650.93017578125</v>
+        <v>7701.47021484375</v>
       </c>
       <c r="C135" t="n">
-        <v>7665.77001953125</v>
+        <v>7707.3798828125</v>
       </c>
       <c r="D135" t="n">
-        <v>7521.9501953125</v>
+        <v>7598.509765625</v>
       </c>
       <c r="E135" t="n">
-        <v>7542.60986328125</v>
+        <v>7688.5</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -3148,19 +3148,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46029</v>
+        <v>46037</v>
       </c>
       <c r="B136" t="n">
-        <v>7574.8701171875</v>
+        <v>7837.2998046875</v>
       </c>
       <c r="C136" t="n">
-        <v>7601.06005859375</v>
+        <v>7998.1201171875</v>
       </c>
       <c r="D136" t="n">
-        <v>7512.85986328125</v>
+        <v>7833.9501953125</v>
       </c>
       <c r="E136" t="n">
-        <v>7554.77978515625</v>
+        <v>7960.9599609375</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -3168,19 +3168,19 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46030</v>
+        <v>46038</v>
       </c>
       <c r="B137" t="n">
-        <v>7436.10009765625</v>
+        <v>7927.41015625</v>
       </c>
       <c r="C137" t="n">
-        <v>7548.31005859375</v>
+        <v>8008.4599609375</v>
       </c>
       <c r="D137" t="n">
-        <v>7372.7900390625</v>
+        <v>7885.91015625</v>
       </c>
       <c r="E137" t="n">
-        <v>7543.25</v>
+        <v>7972.8701171875</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -3188,19 +3188,19 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46031</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>7638.77978515625</v>
+        <v>7794.18994140625</v>
       </c>
       <c r="C138" t="n">
-        <v>7678.89013671875</v>
+        <v>7931.93017578125</v>
       </c>
       <c r="D138" t="n">
-        <v>7467.830078125</v>
+        <v>7767.47998046875</v>
       </c>
       <c r="E138" t="n">
-        <v>7471.330078125</v>
+        <v>7807.89013671875</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -3208,19 +3208,19 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46034</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>7674.83984375</v>
+        <v>8042.06982421875</v>
       </c>
       <c r="C139" t="n">
-        <v>7703.14013671875</v>
+        <v>8113.66015625</v>
       </c>
       <c r="D139" t="n">
-        <v>7568.06982421875</v>
+        <v>7869.72021484375</v>
       </c>
       <c r="E139" t="n">
-        <v>7574.240234375</v>
+        <v>7909.56982421875</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -3228,19 +3228,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46035</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>7747.990234375</v>
+        <v>8055.169921875</v>
       </c>
       <c r="C140" t="n">
-        <v>7825.8798828125</v>
+        <v>8188.16015625</v>
       </c>
       <c r="D140" t="n">
-        <v>7715.8798828125</v>
+        <v>8032.39990234375</v>
       </c>
       <c r="E140" t="n">
-        <v>7725.080078125</v>
+        <v>8186.97021484375</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -3248,19 +3248,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>7701.47021484375</v>
+        <v>7957.93017578125</v>
       </c>
       <c r="C141" t="n">
-        <v>7707.3798828125</v>
+        <v>8032.18994140625</v>
       </c>
       <c r="D141" t="n">
-        <v>7598.509765625</v>
+        <v>7905.14013671875</v>
       </c>
       <c r="E141" t="n">
-        <v>7688.5</v>
+        <v>8024.2099609375</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -3268,19 +3268,19 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>7837.2998046875</v>
+        <v>7927.0400390625</v>
       </c>
       <c r="C142" t="n">
-        <v>7998.1201171875</v>
+        <v>7982.93017578125</v>
       </c>
       <c r="D142" t="n">
-        <v>7833.9501953125</v>
+        <v>7881.43994140625</v>
       </c>
       <c r="E142" t="n">
-        <v>7960.9599609375</v>
+        <v>7917.22998046875</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -3288,19 +3288,19 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46038</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>7927.41015625</v>
+        <v>8117.18017578125</v>
       </c>
       <c r="C143" t="n">
-        <v>8008.4599609375</v>
+        <v>8157.35009765625</v>
       </c>
       <c r="D143" t="n">
-        <v>7885.91015625</v>
+        <v>8009.509765625</v>
       </c>
       <c r="E143" t="n">
-        <v>7972.8701171875</v>
+        <v>8030.39990234375</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -3308,19 +3308,19 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>7794.18994140625</v>
+        <v>8306.740234375</v>
       </c>
       <c r="C144" t="n">
-        <v>7931.93017578125</v>
+        <v>8341.83984375</v>
       </c>
       <c r="D144" t="n">
-        <v>7767.47998046875</v>
+        <v>8227.509765625</v>
       </c>
       <c r="E144" t="n">
-        <v>7807.89013671875</v>
+        <v>8287.4599609375</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -3328,19 +3328,19 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46043</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>8042.06982421875</v>
+        <v>8320.3896484375</v>
       </c>
       <c r="C145" t="n">
-        <v>8113.66015625</v>
+        <v>8386.98046875</v>
       </c>
       <c r="D145" t="n">
-        <v>7869.72021484375</v>
+        <v>8020.93994140625</v>
       </c>
       <c r="E145" t="n">
-        <v>7909.56982421875</v>
+        <v>8340.0400390625</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -3348,19 +3348,19 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>8055.169921875</v>
+        <v>7998.47021484375</v>
       </c>
       <c r="C146" t="n">
-        <v>8188.16015625</v>
+        <v>8309.9599609375</v>
       </c>
       <c r="D146" t="n">
-        <v>8032.39990234375</v>
+        <v>7947.89990234375</v>
       </c>
       <c r="E146" t="n">
-        <v>8186.97021484375</v>
+        <v>8206.3203125</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -3368,19 +3368,19 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>7957.93017578125</v>
+        <v>8134.490234375</v>
       </c>
       <c r="C147" t="n">
-        <v>8032.18994140625</v>
+        <v>8215.400390625</v>
       </c>
       <c r="D147" t="n">
-        <v>7905.14013671875</v>
+        <v>7954.740234375</v>
       </c>
       <c r="E147" t="n">
-        <v>8024.2099609375</v>
+        <v>7955.1201171875</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -3388,19 +3388,19 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>7927.0400390625</v>
+        <v>7966.330078125</v>
       </c>
       <c r="C148" t="n">
-        <v>7982.93017578125</v>
+        <v>8239.6396484375</v>
       </c>
       <c r="D148" t="n">
-        <v>7881.43994140625</v>
+        <v>7796.4599609375</v>
       </c>
       <c r="E148" t="n">
-        <v>7917.22998046875</v>
+        <v>8203.0302734375</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -3408,19 +3408,19 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>8117.18017578125</v>
+        <v>7619.16015625</v>
       </c>
       <c r="C149" t="n">
-        <v>8157.35009765625</v>
+        <v>7955.5</v>
       </c>
       <c r="D149" t="n">
-        <v>8009.509765625</v>
+        <v>7461.740234375</v>
       </c>
       <c r="E149" t="n">
-        <v>8030.39990234375</v>
+        <v>7863.1298828125</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -3428,19 +3428,19 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>8306.740234375</v>
+        <v>7614.64013671875</v>
       </c>
       <c r="C150" t="n">
-        <v>8341.83984375</v>
+        <v>7727.2900390625</v>
       </c>
       <c r="D150" t="n">
-        <v>8227.509765625</v>
+        <v>7473.85009765625</v>
       </c>
       <c r="E150" t="n">
-        <v>8287.4599609375</v>
+        <v>7531.919921875</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -3448,19 +3448,19 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46051</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>8320.3896484375</v>
+        <v>8048.6201171875</v>
       </c>
       <c r="C151" t="n">
-        <v>8386.98046875</v>
+        <v>8071.490234375</v>
       </c>
       <c r="D151" t="n">
-        <v>8020.93994140625</v>
+        <v>7752.5400390625</v>
       </c>
       <c r="E151" t="n">
-        <v>8340.0400390625</v>
+        <v>7762.10986328125</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -3468,19 +3468,19 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46052</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>7998.47021484375</v>
+        <v>8162.580078125</v>
       </c>
       <c r="C152" t="n">
-        <v>8309.9599609375</v>
+        <v>8209.6201171875</v>
       </c>
       <c r="D152" t="n">
-        <v>7947.89990234375</v>
+        <v>7948.52978515625</v>
       </c>
       <c r="E152" t="n">
-        <v>8206.3203125</v>
+        <v>7991.18017578125</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -3488,19 +3488,19 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>8134.490234375</v>
+        <v>8107.1298828125</v>
       </c>
       <c r="C153" t="n">
-        <v>8215.400390625</v>
+        <v>8197.919921875</v>
       </c>
       <c r="D153" t="n">
-        <v>7954.740234375</v>
+        <v>8051.91015625</v>
       </c>
       <c r="E153" t="n">
-        <v>7955.1201171875</v>
+        <v>8191.60986328125</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -3508,19 +3508,19 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46056</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>7966.330078125</v>
+        <v>8291.8603515625</v>
       </c>
       <c r="C154" t="n">
-        <v>8239.6396484375</v>
+        <v>8345.6904296875</v>
       </c>
       <c r="D154" t="n">
-        <v>7796.4599609375</v>
+        <v>8100.580078125</v>
       </c>
       <c r="E154" t="n">
-        <v>8203.0302734375</v>
+        <v>8263.1796875</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -3528,19 +3528,19 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46057</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>7619.16015625</v>
+        <v>8084.7001953125</v>
       </c>
       <c r="C155" t="n">
-        <v>7955.5</v>
+        <v>8400.01953125</v>
       </c>
       <c r="D155" t="n">
-        <v>7461.740234375</v>
+        <v>8079.7900390625</v>
       </c>
       <c r="E155" t="n">
-        <v>7863.1298828125</v>
+        <v>8358.080078125</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -3548,19 +3548,19 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46058</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>7614.64013671875</v>
+        <v>8137.85986328125</v>
       </c>
       <c r="C156" t="n">
-        <v>7727.2900390625</v>
+        <v>8209.3095703125</v>
       </c>
       <c r="D156" t="n">
-        <v>7473.85009765625</v>
+        <v>8010.259765625</v>
       </c>
       <c r="E156" t="n">
-        <v>7531.919921875</v>
+        <v>8090.330078125</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -3568,19 +3568,19 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="B157" t="n">
-        <v>8048.6201171875</v>
+        <v>8136.0498046875</v>
       </c>
       <c r="C157" t="n">
-        <v>8071.490234375</v>
+        <v>8210.51953125</v>
       </c>
       <c r="D157" t="n">
-        <v>7752.5400390625</v>
+        <v>7926.97998046875</v>
       </c>
       <c r="E157" t="n">
-        <v>7762.10986328125</v>
+        <v>8021.990234375</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -3588,19 +3588,19 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46062</v>
+        <v>46071</v>
       </c>
       <c r="B158" t="n">
-        <v>8162.580078125</v>
+        <v>8214.349609375</v>
       </c>
       <c r="C158" t="n">
-        <v>8209.6201171875</v>
+        <v>8303.3203125</v>
       </c>
       <c r="D158" t="n">
-        <v>7948.52978515625</v>
+        <v>8137.5</v>
       </c>
       <c r="E158" t="n">
-        <v>7991.18017578125</v>
+        <v>8170.27978515625</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -3608,19 +3608,19 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46063</v>
+        <v>46072</v>
       </c>
       <c r="B159" t="n">
-        <v>8107.1298828125</v>
+        <v>8173.2998046875</v>
       </c>
       <c r="C159" t="n">
-        <v>8197.919921875</v>
+        <v>8182.39990234375</v>
       </c>
       <c r="D159" t="n">
-        <v>8051.91015625</v>
+        <v>8076.759765625</v>
       </c>
       <c r="E159" t="n">
-        <v>8191.60986328125</v>
+        <v>8133.240234375</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -3628,19 +3628,19 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46064</v>
+        <v>46073</v>
       </c>
       <c r="B160" t="n">
-        <v>8291.8603515625</v>
+        <v>8260.419921875</v>
       </c>
       <c r="C160" t="n">
-        <v>8345.6904296875</v>
+        <v>8308.26953125</v>
       </c>
       <c r="D160" t="n">
-        <v>8100.580078125</v>
+        <v>8106.0400390625</v>
       </c>
       <c r="E160" t="n">
-        <v>8263.1796875</v>
+        <v>8109.0400390625</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -3648,19 +3648,19 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="B161" t="n">
-        <v>8084.7001953125</v>
+        <v>8213.4599609375</v>
       </c>
       <c r="C161" t="n">
-        <v>8400.01953125</v>
+        <v>8291.3896484375</v>
       </c>
       <c r="D161" t="n">
-        <v>8079.7900390625</v>
+        <v>8124.27978515625</v>
       </c>
       <c r="E161" t="n">
-        <v>8358.080078125</v>
+        <v>8248.4404296875</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -3668,19 +3668,19 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="B162" t="n">
-        <v>8137.85986328125</v>
+        <v>8332.33984375</v>
       </c>
       <c r="C162" t="n">
-        <v>8209.3095703125</v>
+        <v>8387.6298828125</v>
       </c>
       <c r="D162" t="n">
-        <v>8010.259765625</v>
+        <v>8225.7197265625</v>
       </c>
       <c r="E162" t="n">
-        <v>8090.330078125</v>
+        <v>8314.740234375</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -3688,19 +3688,19 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46070</v>
+        <v>46078</v>
       </c>
       <c r="B163" t="n">
-        <v>8136.0498046875</v>
+        <v>8467.4296875</v>
       </c>
       <c r="C163" t="n">
-        <v>8210.51953125</v>
+        <v>8498.099609375</v>
       </c>
       <c r="D163" t="n">
-        <v>7926.97998046875</v>
+        <v>8418.509765625</v>
       </c>
       <c r="E163" t="n">
-        <v>8021.990234375</v>
+        <v>8442.849609375</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -3708,19 +3708,19 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="B164" t="n">
-        <v>8214.349609375</v>
+        <v>8197.259765625</v>
       </c>
       <c r="C164" t="n">
-        <v>8303.3203125</v>
+        <v>8422.150390625</v>
       </c>
       <c r="D164" t="n">
-        <v>8137.5</v>
+        <v>8062.10986328125</v>
       </c>
       <c r="E164" t="n">
-        <v>8170.27978515625</v>
+        <v>8402.98046875</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -3728,19 +3728,19 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46072</v>
+        <v>46080</v>
       </c>
       <c r="B165" t="n">
-        <v>8173.2998046875</v>
+        <v>8098.3701171875</v>
       </c>
       <c r="C165" t="n">
-        <v>8182.39990234375</v>
+        <v>8139.990234375</v>
       </c>
       <c r="D165" t="n">
-        <v>8076.759765625</v>
+        <v>8009.25</v>
       </c>
       <c r="E165" t="n">
-        <v>8133.240234375</v>
+        <v>8036.83984375</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -3748,19 +3748,19 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="B166" t="n">
-        <v>8260.419921875</v>
+        <v>8137.35986328125</v>
       </c>
       <c r="C166" t="n">
-        <v>8308.26953125</v>
+        <v>8144.2998046875</v>
       </c>
       <c r="D166" t="n">
-        <v>8106.0400390625</v>
+        <v>7908.759765625</v>
       </c>
       <c r="E166" t="n">
-        <v>8109.0400390625</v>
+        <v>7919.8701171875</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -3768,19 +3768,19 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="B167" t="n">
-        <v>8213.4599609375</v>
+        <v>7764.8798828125</v>
       </c>
       <c r="C167" t="n">
-        <v>8291.3896484375</v>
+        <v>7855.919921875</v>
       </c>
       <c r="D167" t="n">
-        <v>8124.27978515625</v>
+        <v>7673.080078125</v>
       </c>
       <c r="E167" t="n">
-        <v>8248.4404296875</v>
+        <v>7806.2998046875</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -3788,19 +3788,19 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="B168" t="n">
-        <v>8332.33984375</v>
+        <v>7914.47998046875</v>
       </c>
       <c r="C168" t="n">
-        <v>8387.6298828125</v>
+        <v>7959.85009765625</v>
       </c>
       <c r="D168" t="n">
-        <v>8225.7197265625</v>
+        <v>7807.259765625</v>
       </c>
       <c r="E168" t="n">
-        <v>8314.740234375</v>
+        <v>7891.27978515625</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -3808,19 +3808,19 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="B169" t="n">
-        <v>8467.4296875</v>
+        <v>7821.759765625</v>
       </c>
       <c r="C169" t="n">
-        <v>8498.099609375</v>
+        <v>7965.31005859375</v>
       </c>
       <c r="D169" t="n">
-        <v>8418.509765625</v>
+        <v>7660.7001953125</v>
       </c>
       <c r="E169" t="n">
-        <v>8442.849609375</v>
+        <v>7875.93994140625</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -3828,19 +3828,19 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="B170" t="n">
-        <v>8197.259765625</v>
+        <v>7514.740234375</v>
       </c>
       <c r="C170" t="n">
-        <v>8422.150390625</v>
+        <v>7776.72021484375</v>
       </c>
       <c r="D170" t="n">
-        <v>8062.10986328125</v>
+        <v>7466.47021484375</v>
       </c>
       <c r="E170" t="n">
-        <v>8402.98046875</v>
+        <v>7627.68017578125</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -3848,19 +3848,19 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="B171" t="n">
-        <v>8098.3701171875</v>
+        <v>7810.39990234375</v>
       </c>
       <c r="C171" t="n">
-        <v>8139.990234375</v>
+        <v>7826.490234375</v>
       </c>
       <c r="D171" t="n">
-        <v>8009.25</v>
+        <v>7363.169921875</v>
       </c>
       <c r="E171" t="n">
-        <v>8036.83984375</v>
+        <v>7388.330078125</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -3868,19 +3868,19 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="B172" t="n">
-        <v>8137.35986328125</v>
+        <v>7865.1201171875</v>
       </c>
       <c r="C172" t="n">
-        <v>8144.2998046875</v>
+        <v>8017.06005859375</v>
       </c>
       <c r="D172" t="n">
-        <v>7908.759765625</v>
+        <v>7831.10986328125</v>
       </c>
       <c r="E172" t="n">
-        <v>7919.8701171875</v>
+        <v>7846.52978515625</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -3888,19 +3888,19 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46084</v>
+        <v>46092</v>
       </c>
       <c r="B173" t="n">
-        <v>7764.8798828125</v>
+        <v>7914.56982421875</v>
       </c>
       <c r="C173" t="n">
-        <v>7855.919921875</v>
+        <v>8002.93994140625</v>
       </c>
       <c r="D173" t="n">
-        <v>7673.080078125</v>
+        <v>7881.169921875</v>
       </c>
       <c r="E173" t="n">
-        <v>7806.2998046875</v>
+        <v>7918.27978515625</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -3908,19 +3908,19 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B174" t="n">
-        <v>7914.47998046875</v>
+        <v>7643.169921875</v>
       </c>
       <c r="C174" t="n">
-        <v>7959.85009765625</v>
+        <v>7805.25</v>
       </c>
       <c r="D174" t="n">
-        <v>7807.259765625</v>
+        <v>7612.8701171875</v>
       </c>
       <c r="E174" t="n">
-        <v>7891.27978515625</v>
+        <v>7771.490234375</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -3928,19 +3928,19 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="B175" t="n">
-        <v>7821.759765625</v>
+        <v>7646.64013671875</v>
       </c>
       <c r="C175" t="n">
-        <v>7965.31005859375</v>
+        <v>7818.990234375</v>
       </c>
       <c r="D175" t="n">
-        <v>7660.7001953125</v>
+        <v>7617.97998046875</v>
       </c>
       <c r="E175" t="n">
-        <v>7875.93994140625</v>
+        <v>7744.009765625</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
@@ -3948,19 +3948,19 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46087</v>
+        <v>46097</v>
       </c>
       <c r="B176" t="n">
-        <v>7514.740234375</v>
+        <v>7796.240234375</v>
       </c>
       <c r="C176" t="n">
-        <v>7776.72021484375</v>
+        <v>7896.77001953125</v>
       </c>
       <c r="D176" t="n">
-        <v>7466.47021484375</v>
+        <v>7762.06005859375</v>
       </c>
       <c r="E176" t="n">
-        <v>7627.68017578125</v>
+        <v>7846.2900390625</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
@@ -3968,19 +3968,19 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="B177" t="n">
-        <v>7810.39990234375</v>
+        <v>7836.830078125</v>
       </c>
       <c r="C177" t="n">
-        <v>7826.490234375</v>
+        <v>7866.58984375</v>
       </c>
       <c r="D177" t="n">
-        <v>7363.169921875</v>
+        <v>7763.8701171875</v>
       </c>
       <c r="E177" t="n">
-        <v>7388.330078125</v>
+        <v>7828.77001953125</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -3988,19 +3988,19 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46091</v>
+        <v>46099</v>
       </c>
       <c r="B178" t="n">
-        <v>7865.1201171875</v>
+        <v>7795.1298828125</v>
       </c>
       <c r="C178" t="n">
-        <v>8017.06005859375</v>
+        <v>7913.7001953125</v>
       </c>
       <c r="D178" t="n">
-        <v>7831.10986328125</v>
+        <v>7794.259765625</v>
       </c>
       <c r="E178" t="n">
-        <v>7846.52978515625</v>
+        <v>7883.1298828125</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
@@ -4008,19 +4008,19 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="B179" t="n">
-        <v>7914.56982421875</v>
+        <v>7863.2998046875</v>
       </c>
       <c r="C179" t="n">
-        <v>8002.93994140625</v>
+        <v>7913.35009765625</v>
       </c>
       <c r="D179" t="n">
-        <v>7881.169921875</v>
+        <v>7548.5</v>
       </c>
       <c r="E179" t="n">
-        <v>7918.27978515625</v>
+        <v>7561.7998046875</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
@@ -4028,19 +4028,19 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="B180" t="n">
-        <v>7643.169921875</v>
+        <v>7670.60986328125</v>
       </c>
       <c r="C180" t="n">
-        <v>7805.25</v>
+        <v>7880.81005859375</v>
       </c>
       <c r="D180" t="n">
-        <v>7612.8701171875</v>
+        <v>7572.080078125</v>
       </c>
       <c r="E180" t="n">
-        <v>7771.490234375</v>
+        <v>7862.66015625</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -4048,19 +4048,19 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46094</v>
+        <v>46104</v>
       </c>
       <c r="B181" t="n">
-        <v>7646.64013671875</v>
+        <v>7773.1298828125</v>
       </c>
       <c r="C181" t="n">
-        <v>7818.990234375</v>
+        <v>7958</v>
       </c>
       <c r="D181" t="n">
-        <v>7617.97998046875</v>
+        <v>7734.419921875</v>
       </c>
       <c r="E181" t="n">
-        <v>7744.009765625</v>
+        <v>7825.83984375</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -4068,19 +4068,19 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46097</v>
+        <v>46105</v>
       </c>
       <c r="B182" t="n">
-        <v>7796.240234375</v>
+        <v>7872.7099609375</v>
       </c>
       <c r="C182" t="n">
-        <v>7896.77001953125</v>
+        <v>7924.41015625</v>
       </c>
       <c r="D182" t="n">
-        <v>7762.06005859375</v>
+        <v>7709.47998046875</v>
       </c>
       <c r="E182" t="n">
-        <v>7846.2900390625</v>
+        <v>7732.77978515625</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -4088,19 +4088,19 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46098</v>
+        <v>46106</v>
       </c>
       <c r="B183" t="n">
-        <v>7836.830078125</v>
+        <v>7967.75</v>
       </c>
       <c r="C183" t="n">
-        <v>7866.58984375</v>
+        <v>8025.64990234375</v>
       </c>
       <c r="D183" t="n">
-        <v>7763.8701171875</v>
+        <v>7896.240234375</v>
       </c>
       <c r="E183" t="n">
-        <v>7828.77001953125</v>
+        <v>7935.72998046875</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
@@ -4108,19 +4108,19 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="B184" t="n">
-        <v>7795.1298828125</v>
+        <v>7585.8701171875</v>
       </c>
       <c r="C184" t="n">
-        <v>7913.7001953125</v>
+        <v>7831.759765625</v>
       </c>
       <c r="D184" t="n">
-        <v>7794.259765625</v>
+        <v>7582.85986328125</v>
       </c>
       <c r="E184" t="n">
-        <v>7883.1298828125</v>
+        <v>7823.77001953125</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -4128,19 +4128,19 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46100</v>
+        <v>46108</v>
       </c>
       <c r="B185" t="n">
-        <v>7863.2998046875</v>
+        <v>7457.669921875</v>
       </c>
       <c r="C185" t="n">
-        <v>7913.35009765625</v>
+        <v>7611.60009765625</v>
       </c>
       <c r="D185" t="n">
-        <v>7548.5</v>
+        <v>7427.10009765625</v>
       </c>
       <c r="E185" t="n">
-        <v>7561.7998046875</v>
+        <v>7545.419921875</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
@@ -4148,19 +4148,19 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="B186" t="n">
-        <v>7670.60986328125</v>
+        <v>7142.330078125</v>
       </c>
       <c r="C186" t="n">
-        <v>7880.81005859375</v>
+        <v>7546.68017578125</v>
       </c>
       <c r="D186" t="n">
-        <v>7572.080078125</v>
+        <v>7084.1298828125</v>
       </c>
       <c r="E186" t="n">
-        <v>7862.66015625</v>
+        <v>7517.47021484375</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
@@ -4168,19 +4168,19 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="B187" t="n">
-        <v>7773.1298828125</v>
+        <v>7588.2001953125</v>
       </c>
       <c r="C187" t="n">
-        <v>7958</v>
+        <v>7591.330078125</v>
       </c>
       <c r="D187" t="n">
-        <v>7734.419921875</v>
+        <v>7274.14990234375</v>
       </c>
       <c r="E187" t="n">
-        <v>7825.83984375</v>
+        <v>7277.8798828125</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
@@ -4188,19 +4188,19 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="B188" t="n">
-        <v>7872.7099609375</v>
+        <v>7802.31005859375</v>
       </c>
       <c r="C188" t="n">
-        <v>7924.41015625</v>
+        <v>7893.75</v>
       </c>
       <c r="D188" t="n">
-        <v>7709.47998046875</v>
+        <v>7677.5400390625</v>
       </c>
       <c r="E188" t="n">
-        <v>7732.77978515625</v>
+        <v>7680.60986328125</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
@@ -4208,19 +4208,19 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="B189" t="n">
-        <v>7967.75</v>
+        <v>7833.39013671875</v>
       </c>
       <c r="C189" t="n">
-        <v>8025.64990234375</v>
+        <v>7843.740234375</v>
       </c>
       <c r="D189" t="n">
-        <v>7896.240234375</v>
+        <v>7505.97021484375</v>
       </c>
       <c r="E189" t="n">
-        <v>7935.72998046875</v>
+        <v>7544.93017578125</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -4228,19 +4228,19 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46107</v>
+        <v>46118</v>
       </c>
       <c r="B190" t="n">
-        <v>7585.8701171875</v>
+        <v>7916.10986328125</v>
       </c>
       <c r="C190" t="n">
-        <v>7831.759765625</v>
+        <v>7963.64990234375</v>
       </c>
       <c r="D190" t="n">
-        <v>7582.85986328125</v>
+        <v>7821.77978515625</v>
       </c>
       <c r="E190" t="n">
-        <v>7823.77001953125</v>
+        <v>7917.85986328125</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -4248,19 +4248,19 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="B191" t="n">
-        <v>7457.669921875</v>
+        <v>8003.8701171875</v>
       </c>
       <c r="C191" t="n">
-        <v>7611.60009765625</v>
+        <v>8006.33984375</v>
       </c>
       <c r="D191" t="n">
-        <v>7427.10009765625</v>
+        <v>7790.06982421875</v>
       </c>
       <c r="E191" t="n">
-        <v>7545.419921875</v>
+        <v>7915.169921875</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -4268,19 +4268,19 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="B192" t="n">
-        <v>7142.330078125</v>
+        <v>8510.919921875</v>
       </c>
       <c r="C192" t="n">
-        <v>7546.68017578125</v>
+        <v>8526.3896484375</v>
       </c>
       <c r="D192" t="n">
-        <v>7084.1298828125</v>
+        <v>8320.919921875</v>
       </c>
       <c r="E192" t="n">
-        <v>7517.47021484375</v>
+        <v>8497.9296875</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -4288,19 +4288,19 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46112</v>
+        <v>46121</v>
       </c>
       <c r="B193" t="n">
-        <v>7588.2001953125</v>
+        <v>8689.5302734375</v>
       </c>
       <c r="C193" t="n">
-        <v>7591.330078125</v>
+        <v>8699.5</v>
       </c>
       <c r="D193" t="n">
-        <v>7274.14990234375</v>
+        <v>8543.5595703125</v>
       </c>
       <c r="E193" t="n">
-        <v>7277.8798828125</v>
+        <v>8561.1796875</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
@@ -4308,19 +4308,19 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="B194" t="n">
-        <v>7802.31005859375</v>
+        <v>8889.830078125</v>
       </c>
       <c r="C194" t="n">
-        <v>7893.75</v>
+        <v>8962.9501953125</v>
       </c>
       <c r="D194" t="n">
-        <v>7677.5400390625</v>
+        <v>8795.580078125</v>
       </c>
       <c r="E194" t="n">
-        <v>7680.60986328125</v>
+        <v>8812.2197265625</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
@@ -4328,19 +4328,19 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="B195" t="n">
-        <v>7833.39013671875</v>
+        <v>9039.51953125</v>
       </c>
       <c r="C195" t="n">
-        <v>7843.740234375</v>
+        <v>9044.7900390625</v>
       </c>
       <c r="D195" t="n">
-        <v>7505.97021484375</v>
+        <v>8837.9599609375</v>
       </c>
       <c r="E195" t="n">
-        <v>7544.93017578125</v>
+        <v>8873.3095703125</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
@@ -4348,19 +4348,19 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="B196" t="n">
-        <v>7916.10986328125</v>
+        <v>9224.1201171875</v>
       </c>
       <c r="C196" t="n">
-        <v>7963.64990234375</v>
+        <v>9225.4599609375</v>
       </c>
       <c r="D196" t="n">
-        <v>7821.77978515625</v>
+        <v>9042.150390625</v>
       </c>
       <c r="E196" t="n">
-        <v>7917.85986328125</v>
+        <v>9133.2900390625</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
@@ -4368,19 +4368,19 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="B197" t="n">
-        <v>8003.8701171875</v>
+        <v>9239.2900390625</v>
       </c>
       <c r="C197" t="n">
-        <v>8006.33984375</v>
+        <v>9249.9599609375</v>
       </c>
       <c r="D197" t="n">
-        <v>7790.06982421875</v>
+        <v>9035.1103515625</v>
       </c>
       <c r="E197" t="n">
-        <v>7915.169921875</v>
+        <v>9189.23046875</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
@@ -4388,19 +4388,19 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="B198" t="n">
-        <v>8510.919921875</v>
+        <v>9329.349609375</v>
       </c>
       <c r="C198" t="n">
-        <v>8526.3896484375</v>
+        <v>9356.16015625</v>
       </c>
       <c r="D198" t="n">
-        <v>8320.919921875</v>
+        <v>9144.98046875</v>
       </c>
       <c r="E198" t="n">
-        <v>8497.9296875</v>
+        <v>9215.9296875</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
@@ -4408,19 +4408,19 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="B199" t="n">
-        <v>8689.5302734375</v>
+        <v>9555.8798828125</v>
       </c>
       <c r="C199" t="n">
-        <v>8699.5</v>
+        <v>9556.419921875</v>
       </c>
       <c r="D199" t="n">
-        <v>8543.5595703125</v>
+        <v>9419.1298828125</v>
       </c>
       <c r="E199" t="n">
-        <v>8561.1796875</v>
+        <v>9477.8896484375</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
@@ -4428,19 +4428,19 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="B200" t="n">
-        <v>8889.830078125</v>
+        <v>9599.2099609375</v>
       </c>
       <c r="C200" t="n">
-        <v>8962.9501953125</v>
+        <v>9612.08984375</v>
       </c>
       <c r="D200" t="n">
-        <v>8795.580078125</v>
+        <v>9462.9404296875</v>
       </c>
       <c r="E200" t="n">
-        <v>8812.2197265625</v>
+        <v>9604.900390625</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -4448,19 +4448,19 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="B201" t="n">
-        <v>9039.51953125</v>
+        <v>9647.2099609375</v>
       </c>
       <c r="C201" t="n">
-        <v>9044.7900390625</v>
+        <v>9721.400390625</v>
       </c>
       <c r="D201" t="n">
-        <v>8837.9599609375</v>
+        <v>9569.7001953125</v>
       </c>
       <c r="E201" t="n">
-        <v>8873.3095703125</v>
+        <v>9676.7802734375</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
@@ -4468,19 +4468,19 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="B202" t="n">
-        <v>9224.1201171875</v>
+        <v>9909.26953125</v>
       </c>
       <c r="C202" t="n">
-        <v>9225.4599609375</v>
+        <v>9914.080078125</v>
       </c>
       <c r="D202" t="n">
-        <v>9042.150390625</v>
+        <v>9698.9501953125</v>
       </c>
       <c r="E202" t="n">
-        <v>9133.2900390625</v>
+        <v>9817.099609375</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
@@ -4488,19 +4488,19 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="B203" t="n">
-        <v>9239.2900390625</v>
+        <v>10078.5703125</v>
       </c>
       <c r="C203" t="n">
-        <v>9249.9599609375</v>
+        <v>10206.1796875</v>
       </c>
       <c r="D203" t="n">
-        <v>9035.1103515625</v>
+        <v>9923.4296875</v>
       </c>
       <c r="E203" t="n">
-        <v>9189.23046875</v>
+        <v>9984.73046875</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -4508,19 +4508,19 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="B204" t="n">
-        <v>9329.349609375</v>
+        <v>10513.66015625</v>
       </c>
       <c r="C204" t="n">
-        <v>9356.16015625</v>
+        <v>10564.009765625</v>
       </c>
       <c r="D204" t="n">
-        <v>9144.98046875</v>
+        <v>10270.9599609375</v>
       </c>
       <c r="E204" t="n">
-        <v>9215.9296875</v>
+        <v>10463.8095703125</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
@@ -4528,19 +4528,19 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46129</v>
+        <v>46139</v>
       </c>
       <c r="B205" t="n">
-        <v>9555.8798828125</v>
+        <v>10408.0400390625</v>
       </c>
       <c r="C205" t="n">
-        <v>9556.419921875</v>
+        <v>10536.8603515625</v>
       </c>
       <c r="D205" t="n">
-        <v>9419.1298828125</v>
+        <v>10251.73046875</v>
       </c>
       <c r="E205" t="n">
-        <v>9477.8896484375</v>
+        <v>10533.3203125</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -4548,19 +4548,19 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="B206" t="n">
-        <v>9599.2099609375</v>
+        <v>10035.580078125</v>
       </c>
       <c r="C206" t="n">
-        <v>9612.08984375</v>
+        <v>10184.990234375</v>
       </c>
       <c r="D206" t="n">
-        <v>9462.9404296875</v>
+        <v>9865.3798828125</v>
       </c>
       <c r="E206" t="n">
-        <v>9604.900390625</v>
+        <v>9979.169921875</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
@@ -4568,19 +4568,19 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="B207" t="n">
-        <v>9647.2099609375</v>
+        <v>10271.2998046875</v>
       </c>
       <c r="C207" t="n">
-        <v>9721.400390625</v>
+        <v>10272.9501953125</v>
       </c>
       <c r="D207" t="n">
-        <v>9569.7001953125</v>
+        <v>10113.2099609375</v>
       </c>
       <c r="E207" t="n">
-        <v>9676.7802734375</v>
+        <v>10192.330078125</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
@@ -4588,19 +4588,19 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="B208" t="n">
-        <v>9909.26953125</v>
+        <v>10503.7001953125</v>
       </c>
       <c r="C208" t="n">
-        <v>9914.080078125</v>
+        <v>10516.3896484375</v>
       </c>
       <c r="D208" t="n">
-        <v>9698.9501953125</v>
+        <v>10229.8896484375</v>
       </c>
       <c r="E208" t="n">
-        <v>9817.099609375</v>
+        <v>10387.83984375</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
@@ -4608,19 +4608,19 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="B209" t="n">
-        <v>10078.5703125</v>
+        <v>10595.33984375</v>
       </c>
       <c r="C209" t="n">
-        <v>10206.1796875</v>
+        <v>10624.2099609375</v>
       </c>
       <c r="D209" t="n">
-        <v>9923.4296875</v>
+        <v>10364.400390625</v>
       </c>
       <c r="E209" t="n">
-        <v>9984.73046875</v>
+        <v>10388.8203125</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -4628,19 +4628,19 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="B210" t="n">
-        <v>10513.66015625</v>
+        <v>10534.66015625</v>
       </c>
       <c r="C210" t="n">
-        <v>10564.009765625</v>
+        <v>10690.4697265625</v>
       </c>
       <c r="D210" t="n">
-        <v>10270.9599609375</v>
+        <v>10430.2099609375</v>
       </c>
       <c r="E210" t="n">
-        <v>10463.8095703125</v>
+        <v>10656.0703125</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -4648,19 +4648,19 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="B211" t="n">
-        <v>10408.0400390625</v>
+        <v>10980.580078125</v>
       </c>
       <c r="C211" t="n">
-        <v>10536.8603515625</v>
+        <v>11058.16015625</v>
       </c>
       <c r="D211" t="n">
-        <v>10251.73046875</v>
+        <v>10718.490234375</v>
       </c>
       <c r="E211" t="n">
-        <v>10533.3203125</v>
+        <v>10759.2099609375</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
@@ -4668,19 +4668,19 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="B212" t="n">
-        <v>10035.580078125</v>
+        <v>11472.75</v>
       </c>
       <c r="C212" t="n">
-        <v>10184.990234375</v>
+        <v>11477.3798828125</v>
       </c>
       <c r="D212" t="n">
-        <v>9865.3798828125</v>
+        <v>11062.9501953125</v>
       </c>
       <c r="E212" t="n">
-        <v>9979.169921875</v>
+        <v>11243.830078125</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -4688,19 +4688,19 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="B213" t="n">
-        <v>10271.2998046875</v>
+        <v>11160.990234375</v>
       </c>
       <c r="C213" t="n">
-        <v>10272.9501953125</v>
+        <v>11404.3701171875</v>
       </c>
       <c r="D213" t="n">
-        <v>10113.2099609375</v>
+        <v>11075.1298828125</v>
       </c>
       <c r="E213" t="n">
-        <v>10192.330078125</v>
+        <v>11332.1904296875</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
@@ -4708,19 +4708,19 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="B214" t="n">
-        <v>10503.7001953125</v>
+        <v>11775.5</v>
       </c>
       <c r="C214" t="n">
-        <v>10516.3896484375</v>
+        <v>11776.740234375</v>
       </c>
       <c r="D214" t="n">
-        <v>10229.8896484375</v>
+        <v>11388.419921875</v>
       </c>
       <c r="E214" t="n">
-        <v>10387.83984375</v>
+        <v>11408.009765625</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
@@ -4728,19 +4728,19 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="B215" t="n">
-        <v>10595.33984375</v>
+        <v>12081.0400390625</v>
       </c>
       <c r="C215" t="n">
-        <v>10624.2099609375</v>
+        <v>12108.669921875</v>
       </c>
       <c r="D215" t="n">
-        <v>10364.400390625</v>
+        <v>11822.490234375</v>
       </c>
       <c r="E215" t="n">
-        <v>10388.8203125</v>
+        <v>11875.2900390625</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
@@ -4748,19 +4748,19 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="B216" t="n">
-        <v>10534.66015625</v>
+        <v>11717.259765625</v>
       </c>
       <c r="C216" t="n">
-        <v>10690.4697265625</v>
+        <v>11919</v>
       </c>
       <c r="D216" t="n">
-        <v>10430.2099609375</v>
+        <v>11263.580078125</v>
       </c>
       <c r="E216" t="n">
-        <v>10656.0703125</v>
+        <v>11741.4697265625</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -4768,19 +4768,19 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="B217" t="n">
-        <v>10980.580078125</v>
+        <v>12017.98046875</v>
       </c>
       <c r="C217" t="n">
-        <v>11058.16015625</v>
+        <v>12106.5498046875</v>
       </c>
       <c r="D217" t="n">
-        <v>10718.490234375</v>
+        <v>11739.169921875</v>
       </c>
       <c r="E217" t="n">
-        <v>10759.2099609375</v>
+        <v>11988.75</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -4788,19 +4788,19 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="B218" t="n">
-        <v>11472.75</v>
+        <v>12073.7802734375</v>
       </c>
       <c r="C218" t="n">
-        <v>11477.3798828125</v>
+        <v>12141.5400390625</v>
       </c>
       <c r="D218" t="n">
-        <v>11062.9501953125</v>
+        <v>11892.41015625</v>
       </c>
       <c r="E218" t="n">
-        <v>11243.830078125</v>
+        <v>11950.1396484375</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -4808,19 +4808,19 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="B219" t="n">
-        <v>11160.990234375</v>
+        <v>11588.4599609375</v>
       </c>
       <c r="C219" t="n">
-        <v>11404.3701171875</v>
+        <v>11810.669921875</v>
       </c>
       <c r="D219" t="n">
-        <v>11075.1298828125</v>
+        <v>11522.26953125</v>
       </c>
       <c r="E219" t="n">
-        <v>11332.1904296875</v>
+        <v>11672.5400390625</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -4828,19 +4828,19 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="B220" t="n">
-        <v>11775.5</v>
+        <v>11302.51953125</v>
       </c>
       <c r="C220" t="n">
-        <v>11776.740234375</v>
+        <v>11825.8798828125</v>
       </c>
       <c r="D220" t="n">
-        <v>11388.419921875</v>
+        <v>11097.759765625</v>
       </c>
       <c r="E220" t="n">
-        <v>11408.009765625</v>
+        <v>11825.8798828125</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
@@ -4848,19 +4848,19 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B221" t="n">
-        <v>12081.0400390625</v>
+        <v>11305.5</v>
       </c>
       <c r="C221" t="n">
-        <v>12108.669921875</v>
+        <v>11513.990234375</v>
       </c>
       <c r="D221" t="n">
-        <v>11822.490234375</v>
+        <v>10895.75</v>
       </c>
       <c r="E221" t="n">
-        <v>11875.2900390625</v>
+        <v>11053.990234375</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
@@ -4868,19 +4868,19 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B222" t="n">
-        <v>11717.259765625</v>
+        <v>11813.2900390625</v>
       </c>
       <c r="C222" t="n">
-        <v>11919</v>
+        <v>11818.3896484375</v>
       </c>
       <c r="D222" t="n">
-        <v>11263.580078125</v>
+        <v>11528.1298828125</v>
       </c>
       <c r="E222" t="n">
-        <v>11741.4697265625</v>
+        <v>11580.080078125</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -4888,19 +4888,19 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B223" t="n">
-        <v>12017.98046875</v>
+        <v>11964.080078125</v>
       </c>
       <c r="C223" t="n">
-        <v>12106.5498046875</v>
+        <v>12003.009765625</v>
       </c>
       <c r="D223" t="n">
-        <v>11739.169921875</v>
+        <v>11739.8095703125</v>
       </c>
       <c r="E223" t="n">
-        <v>11988.75</v>
+        <v>11826.08984375</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
@@ -4908,19 +4908,19 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B224" t="n">
-        <v>12073.7802734375</v>
+        <v>12202.5400390625</v>
       </c>
       <c r="C224" t="n">
-        <v>12141.5400390625</v>
+        <v>12304.51953125</v>
       </c>
       <c r="D224" t="n">
-        <v>11892.41015625</v>
+        <v>12069.0400390625</v>
       </c>
       <c r="E224" t="n">
-        <v>11950.1396484375</v>
+        <v>12070.169921875</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
@@ -4928,19 +4928,19 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B225" t="n">
-        <v>11588.4599609375</v>
+        <v>12876.91015625</v>
       </c>
       <c r="C225" t="n">
-        <v>11810.669921875</v>
+        <v>12932.8095703125</v>
       </c>
       <c r="D225" t="n">
-        <v>11522.26953125</v>
+        <v>12548.240234375</v>
       </c>
       <c r="E225" t="n">
-        <v>11672.5400390625</v>
+        <v>12616.6298828125</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -4948,19 +4948,19 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B226" t="n">
-        <v>11302.51953125</v>
+        <v>12702.1904296875</v>
       </c>
       <c r="C226" t="n">
-        <v>11825.8798828125</v>
+        <v>13037.91015625</v>
       </c>
       <c r="D226" t="n">
-        <v>11097.759765625</v>
+        <v>12452.3603515625</v>
       </c>
       <c r="E226" t="n">
-        <v>11825.8798828125</v>
+        <v>13029.7900390625</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
@@ -4968,19 +4968,19 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="B227" t="n">
-        <v>11305.5</v>
+        <v>12829.1396484375</v>
       </c>
       <c r="C227" t="n">
-        <v>11513.990234375</v>
+        <v>12961.1904296875</v>
       </c>
       <c r="D227" t="n">
-        <v>10895.75</v>
+        <v>12528.6904296875</v>
       </c>
       <c r="E227" t="n">
-        <v>11053.990234375</v>
+        <v>12748.58984375</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -4988,19 +4988,19 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B228" t="n">
-        <v>11813.2900390625</v>
+        <v>12829.3798828125</v>
       </c>
       <c r="C228" t="n">
-        <v>11818.3896484375</v>
+        <v>13115.2802734375</v>
       </c>
       <c r="D228" t="n">
-        <v>11528.1298828125</v>
+        <v>12737.1904296875</v>
       </c>
       <c r="E228" t="n">
-        <v>11580.080078125</v>
+        <v>12973.76953125</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -5008,19 +5008,19 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46163</v>
+        <v>46174</v>
       </c>
       <c r="B229" t="n">
-        <v>11964.080078125</v>
+        <v>12965.650390625</v>
       </c>
       <c r="C229" t="n">
-        <v>12003.009765625</v>
+        <v>13088.009765625</v>
       </c>
       <c r="D229" t="n">
-        <v>11739.8095703125</v>
+        <v>12631.0302734375</v>
       </c>
       <c r="E229" t="n">
-        <v>11826.08984375</v>
+        <v>12706.6201171875</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -5028,19 +5028,19 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46164</v>
+        <v>46175</v>
       </c>
       <c r="B230" t="n">
-        <v>12202.5400390625</v>
+        <v>13726.26953125</v>
       </c>
       <c r="C230" t="n">
-        <v>12304.51953125</v>
+        <v>13733.7197265625</v>
       </c>
       <c r="D230" t="n">
-        <v>12069.0400390625</v>
+        <v>13202.1796875</v>
       </c>
       <c r="E230" t="n">
-        <v>12070.169921875</v>
+        <v>13242.7001953125</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
@@ -5048,19 +5048,19 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46176</v>
       </c>
       <c r="B231" t="n">
-        <v>12876.91015625</v>
+        <v>13916.9599609375</v>
       </c>
       <c r="C231" t="n">
-        <v>12932.8095703125</v>
+        <v>13998.1396484375</v>
       </c>
       <c r="D231" t="n">
-        <v>12548.240234375</v>
+        <v>13554.3701171875</v>
       </c>
       <c r="E231" t="n">
-        <v>12616.6298828125</v>
+        <v>13971.150390625</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -5068,19 +5068,19 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="B232" t="n">
-        <v>12702.1904296875</v>
+        <v>13617.5</v>
       </c>
       <c r="C232" t="n">
-        <v>13037.91015625</v>
+        <v>13819.6201171875</v>
       </c>
       <c r="D232" t="n">
-        <v>12452.3603515625</v>
+        <v>13041.2802734375</v>
       </c>
       <c r="E232" t="n">
-        <v>13029.7900390625</v>
+        <v>13243.66015625</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -5088,19 +5088,19 @@
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="B233" t="n">
-        <v>12829.1396484375</v>
+        <v>12220.759765625</v>
       </c>
       <c r="C233" t="n">
-        <v>12961.1904296875</v>
+        <v>13111.4404296875</v>
       </c>
       <c r="D233" t="n">
-        <v>12528.6904296875</v>
+        <v>12217.3203125</v>
       </c>
       <c r="E233" t="n">
-        <v>12748.58984375</v>
+        <v>13062.5498046875</v>
       </c>
       <c r="F233" t="n">
         <v>0</v>
@@ -5108,19 +5108,19 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="B234" t="n">
-        <v>12829.3798828125</v>
+        <v>12906.6904296875</v>
       </c>
       <c r="C234" t="n">
-        <v>13115.2802734375</v>
+        <v>13129.01953125</v>
       </c>
       <c r="D234" t="n">
-        <v>12737.1904296875</v>
+        <v>12676.740234375</v>
       </c>
       <c r="E234" t="n">
-        <v>12973.76953125</v>
+        <v>12838.8798828125</v>
       </c>
       <c r="F234" t="n">
         <v>0</v>
@@ -5128,19 +5128,19 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B235" t="n">
-        <v>12965.650390625</v>
+        <v>12657.8095703125</v>
       </c>
       <c r="C235" t="n">
-        <v>13088.009765625</v>
+        <v>13264.1201171875</v>
       </c>
       <c r="D235" t="n">
-        <v>12631.0302734375</v>
+        <v>11794.150390625</v>
       </c>
       <c r="E235" t="n">
-        <v>12706.6201171875</v>
+        <v>13142.990234375</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -5148,19 +5148,19 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="B236" t="n">
-        <v>13726.26953125</v>
+        <v>12206.4599609375</v>
       </c>
       <c r="C236" t="n">
-        <v>13733.7197265625</v>
+        <v>12870.5302734375</v>
       </c>
       <c r="D236" t="n">
-        <v>13202.1796875</v>
+        <v>12157.66015625</v>
       </c>
       <c r="E236" t="n">
-        <v>13242.7001953125</v>
+        <v>12501.83984375</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -5168,19 +5168,19 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B237" t="n">
-        <v>13916.9599609375</v>
+        <v>13171.4404296875</v>
       </c>
       <c r="C237" t="n">
-        <v>13998.1396484375</v>
+        <v>13194.2802734375</v>
       </c>
       <c r="D237" t="n">
-        <v>13554.3701171875</v>
+        <v>12475.23046875</v>
       </c>
       <c r="E237" t="n">
-        <v>13971.150390625</v>
+        <v>12506.650390625</v>
       </c>
       <c r="F237" t="n">
         <v>0</v>
@@ -5188,19 +5188,19 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B238" t="n">
-        <v>13617.5</v>
+        <v>13371.4697265625</v>
       </c>
       <c r="C238" t="n">
-        <v>13819.6201171875</v>
+        <v>13513.4404296875</v>
       </c>
       <c r="D238" t="n">
-        <v>13041.2802734375</v>
+        <v>12986.0595703125</v>
       </c>
       <c r="E238" t="n">
-        <v>13243.66015625</v>
+        <v>13053.9296875</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -5208,19 +5208,19 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46178</v>
+        <v>46188</v>
       </c>
       <c r="B239" t="n">
-        <v>12220.759765625</v>
+        <v>14099.6201171875</v>
       </c>
       <c r="C239" t="n">
-        <v>13111.4404296875</v>
+        <v>14134.599609375</v>
       </c>
       <c r="D239" t="n">
-        <v>12217.3203125</v>
+        <v>13860.3203125</v>
       </c>
       <c r="E239" t="n">
-        <v>13062.5498046875</v>
+        <v>13901.240234375</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="B240" t="n">
-        <v>12906.6904296875</v>
+        <v>13294.2197265625</v>
       </c>
       <c r="C240" t="n">
-        <v>13129.01953125</v>
+        <v>14133.599609375</v>
       </c>
       <c r="D240" t="n">
-        <v>12676.740234375</v>
+        <v>13291.75</v>
       </c>
       <c r="E240" t="n">
-        <v>12838.8798828125</v>
+        <v>13968.2802734375</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -5248,19 +5248,19 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="B241" t="n">
-        <v>12657.8095703125</v>
+        <v>13477.0703125</v>
       </c>
       <c r="C241" t="n">
-        <v>13264.1201171875</v>
+        <v>13965.599609375</v>
       </c>
       <c r="D241" t="n">
-        <v>11794.150390625</v>
+        <v>13471.2197265625</v>
       </c>
       <c r="E241" t="n">
-        <v>13142.990234375</v>
+        <v>13694.009765625</v>
       </c>
       <c r="F241" t="n">
         <v>0</v>
@@ -5268,19 +5268,19 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="B242" t="n">
-        <v>12206.4599609375</v>
+        <v>14341.7802734375</v>
       </c>
       <c r="C242" t="n">
-        <v>12870.5302734375</v>
+        <v>14461.7900390625</v>
       </c>
       <c r="D242" t="n">
-        <v>12157.66015625</v>
+        <v>14062.2802734375</v>
       </c>
       <c r="E242" t="n">
-        <v>12501.83984375</v>
+        <v>14084.759765625</v>
       </c>
       <c r="F242" t="n">
         <v>0</v>
@@ -5288,19 +5288,19 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="B243" t="n">
-        <v>13171.4404296875</v>
+        <v>14634.7197265625</v>
       </c>
       <c r="C243" t="n">
-        <v>13194.2802734375</v>
+        <v>14655.2900390625</v>
       </c>
       <c r="D243" t="n">
-        <v>12475.23046875</v>
+        <v>14393.8896484375</v>
       </c>
       <c r="E243" t="n">
-        <v>12506.650390625</v>
+        <v>14607.0498046875</v>
       </c>
       <c r="F243" t="n">
         <v>0</v>
@@ -5308,19 +5308,19 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="B244" t="n">
-        <v>13371.4697265625</v>
+        <v>13482.509765625</v>
       </c>
       <c r="C244" t="n">
-        <v>13513.4404296875</v>
+        <v>13857.16015625</v>
       </c>
       <c r="D244" t="n">
-        <v>12986.0595703125</v>
+        <v>13374.4404296875</v>
       </c>
       <c r="E244" t="n">
-        <v>13053.9296875</v>
+        <v>13586.2900390625</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
@@ -5328,19 +5328,19 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="B245" t="n">
-        <v>14099.6201171875</v>
+        <v>13458.2001953125</v>
       </c>
       <c r="C245" t="n">
-        <v>14134.599609375</v>
+        <v>13597.3798828125</v>
       </c>
       <c r="D245" t="n">
-        <v>13860.3203125</v>
+        <v>13115.830078125</v>
       </c>
       <c r="E245" t="n">
-        <v>13901.240234375</v>
+        <v>13484.169921875</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -5348,19 +5348,19 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="B246" t="n">
-        <v>13294.2197265625</v>
+        <v>13940.8701171875</v>
       </c>
       <c r="C246" t="n">
-        <v>14133.599609375</v>
+        <v>14194.6796875</v>
       </c>
       <c r="D246" t="n">
-        <v>13291.75</v>
+        <v>13379.9404296875</v>
       </c>
       <c r="E246" t="n">
-        <v>13968.2802734375</v>
+        <v>14156.4296875</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -5368,19 +5368,19 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="B247" t="n">
-        <v>13477.0703125</v>
+        <v>13203.5703125</v>
       </c>
       <c r="C247" t="n">
-        <v>13965.599609375</v>
+        <v>13519.5498046875</v>
       </c>
       <c r="D247" t="n">
-        <v>13471.2197265625</v>
+        <v>13159.240234375</v>
       </c>
       <c r="E247" t="n">
-        <v>13694.009765625</v>
+        <v>13419.1396484375</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -5388,19 +5388,19 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="B248" t="n">
-        <v>14341.7802734375</v>
+        <v>13709.66015625</v>
       </c>
       <c r="C248" t="n">
-        <v>14461.7900390625</v>
+        <v>13733.349609375</v>
       </c>
       <c r="D248" t="n">
-        <v>14062.2802734375</v>
+        <v>12782.5302734375</v>
       </c>
       <c r="E248" t="n">
-        <v>14084.759765625</v>
+        <v>13241.9697265625</v>
       </c>
       <c r="F248" t="n">
         <v>0</v>
@@ -5408,19 +5408,19 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B249" t="n">
-        <v>14634.7197265625</v>
+        <v>14246.9599609375</v>
       </c>
       <c r="C249" t="n">
-        <v>14655.2900390625</v>
+        <v>14332.759765625</v>
       </c>
       <c r="D249" t="n">
-        <v>14393.8896484375</v>
+        <v>13750.669921875</v>
       </c>
       <c r="E249" t="n">
-        <v>14607.0498046875</v>
+        <v>13787.919921875</v>
       </c>
       <c r="F249" t="n">
         <v>0</v>
@@ -5428,19 +5428,19 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="B250" t="n">
-        <v>13482.509765625</v>
+        <v>13353.2802734375</v>
       </c>
       <c r="C250" t="n">
-        <v>13857.16015625</v>
+        <v>13844.419921875</v>
       </c>
       <c r="D250" t="n">
-        <v>13374.4404296875</v>
+        <v>13322.6298828125</v>
       </c>
       <c r="E250" t="n">
-        <v>13586.2900390625</v>
+        <v>13718.080078125</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -5448,19 +5448,19 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46205</v>
       </c>
       <c r="B251" t="n">
-        <v>13458.2001953125</v>
+        <v>12626.2197265625</v>
       </c>
       <c r="C251" t="n">
-        <v>13597.3798828125</v>
+        <v>13526.7197265625</v>
       </c>
       <c r="D251" t="n">
-        <v>13115.830078125</v>
+        <v>12374.41015625</v>
       </c>
       <c r="E251" t="n">
-        <v>13484.169921875</v>
+        <v>13268.2197265625</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
@@ -5468,19 +5468,19 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="B252" t="n">
-        <v>13940.8701171875</v>
+        <v>12900.1416015625</v>
       </c>
       <c r="C252" t="n">
-        <v>14194.6767578125</v>
+        <v>13252.544921875</v>
       </c>
       <c r="D252" t="n">
-        <v>13379.943359375</v>
+        <v>12890.6162109375</v>
       </c>
       <c r="E252" t="n">
-        <v>14156.4345703125</v>
+        <v>12914.470703125</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
